--- a/data/raw/NVDA.xlsx
+++ b/data/raw/NVDA.xlsx
@@ -468,5022 +468,5022 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45834</v>
+        <v>45845</v>
       </c>
       <c r="B2" t="n">
-        <v>154.8138122558594</v>
+        <v>158.0295257568359</v>
       </c>
       <c r="C2" t="n">
-        <v>156.5115480391595</v>
+        <v>159.0980945940048</v>
       </c>
       <c r="D2" t="n">
-        <v>153.7951646904819</v>
+        <v>157.1307137305003</v>
       </c>
       <c r="E2" t="n">
-        <v>155.7725268268671</v>
+        <v>157.9895704284692</v>
       </c>
       <c r="F2" t="n">
-        <v>198145700</v>
+        <v>140139000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45835</v>
+        <v>45846</v>
       </c>
       <c r="B3" t="n">
-        <v>157.5401611328125</v>
+        <v>159.7871856689453</v>
       </c>
       <c r="C3" t="n">
-        <v>158.4988908468614</v>
+        <v>160.0068942683196</v>
       </c>
       <c r="D3" t="n">
-        <v>155.0534678420698</v>
+        <v>158.1793265036118</v>
       </c>
       <c r="E3" t="n">
-        <v>155.8324290678944</v>
+        <v>159.1180786575758</v>
       </c>
       <c r="F3" t="n">
-        <v>263234500</v>
+        <v>138133000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45838</v>
+        <v>45847</v>
       </c>
       <c r="B4" t="n">
-        <v>157.7798461914062</v>
+        <v>162.6633453369141</v>
       </c>
       <c r="C4" t="n">
-        <v>158.4489531245615</v>
+        <v>164.2012901564699</v>
       </c>
       <c r="D4" t="n">
-        <v>155.7525477292889</v>
+        <v>160.9456320255445</v>
       </c>
       <c r="E4" t="n">
-        <v>158.1892892255667</v>
+        <v>161.0055497766517</v>
       </c>
       <c r="F4" t="n">
-        <v>194580300</v>
+        <v>183656400</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45839</v>
+        <v>45848</v>
       </c>
       <c r="B5" t="n">
-        <v>153.0960998535156</v>
+        <v>163.8817291259766</v>
       </c>
       <c r="C5" t="n">
-        <v>156.9909063970138</v>
+        <v>164.2811909721531</v>
       </c>
       <c r="D5" t="n">
-        <v>151.2885097592641</v>
+        <v>161.3950357038234</v>
       </c>
       <c r="E5" t="n">
-        <v>156.0821131240331</v>
+        <v>164.1014377129215</v>
       </c>
       <c r="F5" t="n">
-        <v>213143600</v>
+        <v>167704100</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45840</v>
+        <v>45849</v>
       </c>
       <c r="B6" t="n">
-        <v>157.0408477783203</v>
+        <v>164.7006225585938</v>
       </c>
       <c r="C6" t="n">
-        <v>157.3903883520798</v>
+        <v>167.6666731011634</v>
       </c>
       <c r="D6" t="n">
-        <v>152.7665416620026</v>
+        <v>163.2525543877531</v>
       </c>
       <c r="E6" t="n">
-        <v>152.7765228755266</v>
+        <v>163.5022218392253</v>
       </c>
       <c r="F6" t="n">
-        <v>171224100</v>
+        <v>193633300</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45841</v>
+        <v>45852</v>
       </c>
       <c r="B7" t="n">
-        <v>159.1280517578125</v>
+        <v>163.8517608642578</v>
       </c>
       <c r="C7" t="n">
-        <v>160.7658697178767</v>
+        <v>165.2698701469979</v>
       </c>
       <c r="D7" t="n">
-        <v>157.5601480023909</v>
+        <v>161.8044847332593</v>
       </c>
       <c r="E7" t="n">
-        <v>158.159340775004</v>
+        <v>165.1500194092157</v>
       </c>
       <c r="F7" t="n">
-        <v>143716100</v>
+        <v>136975800</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45845</v>
+        <v>45853</v>
       </c>
       <c r="B8" t="n">
-        <v>158.0295104980469</v>
+        <v>170.4729461669922</v>
       </c>
       <c r="C8" t="n">
-        <v>159.0980792320384</v>
+        <v>172.1706819222518</v>
       </c>
       <c r="D8" t="n">
-        <v>157.1306985584975</v>
+        <v>168.9749413408526</v>
       </c>
       <c r="E8" t="n">
-        <v>157.9895551735382</v>
+        <v>170.9622998960553</v>
       </c>
       <c r="F8" t="n">
-        <v>140139000</v>
+        <v>230627400</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45846</v>
+        <v>45854</v>
       </c>
       <c r="B9" t="n">
-        <v>159.7871856689453</v>
+        <v>171.1420593261719</v>
       </c>
       <c r="C9" t="n">
-        <v>160.0068942683196</v>
+        <v>171.5215587721167</v>
       </c>
       <c r="D9" t="n">
-        <v>158.1793265036118</v>
+        <v>168.6753434045181</v>
       </c>
       <c r="E9" t="n">
-        <v>159.1180786575758</v>
+        <v>170.832474089109</v>
       </c>
       <c r="F9" t="n">
-        <v>138133000</v>
+        <v>158831500</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45847</v>
+        <v>45855</v>
       </c>
       <c r="B10" t="n">
-        <v>162.6633453369141</v>
+        <v>172.7698974609375</v>
       </c>
       <c r="C10" t="n">
-        <v>164.2012901564699</v>
+        <v>173.9283582340991</v>
       </c>
       <c r="D10" t="n">
-        <v>160.9456320255445</v>
+        <v>170.6027855468386</v>
       </c>
       <c r="E10" t="n">
-        <v>161.0055497766517</v>
+        <v>171.7912051987463</v>
       </c>
       <c r="F10" t="n">
-        <v>183656400</v>
+        <v>160841100</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45848</v>
+        <v>45856</v>
       </c>
       <c r="B11" t="n">
-        <v>163.8817443847656</v>
+        <v>172.1806793212891</v>
       </c>
       <c r="C11" t="n">
-        <v>164.2812062681355</v>
+        <v>174.0182282608946</v>
       </c>
       <c r="D11" t="n">
-        <v>161.3950507310801</v>
+        <v>171.0321998051657</v>
       </c>
       <c r="E11" t="n">
-        <v>164.1014529921673</v>
+        <v>173.4090390187055</v>
       </c>
       <c r="F11" t="n">
-        <v>167704100</v>
+        <v>146456400</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45849</v>
+        <v>45859</v>
       </c>
       <c r="B12" t="n">
-        <v>164.7006378173828</v>
+        <v>171.1520538330078</v>
       </c>
       <c r="C12" t="n">
-        <v>167.666688634744</v>
+        <v>173.1493936504508</v>
       </c>
       <c r="D12" t="n">
-        <v>163.252569512385</v>
+        <v>170.7725543913757</v>
       </c>
       <c r="E12" t="n">
-        <v>163.5022369869878</v>
+        <v>172.5202267316384</v>
       </c>
       <c r="F12" t="n">
-        <v>193633300</v>
+        <v>123126100</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45852</v>
+        <v>45860</v>
       </c>
       <c r="B13" t="n">
-        <v>163.8517761230469</v>
+        <v>166.8078308105469</v>
       </c>
       <c r="C13" t="n">
-        <v>165.2698855378492</v>
+        <v>171.1620321483939</v>
       </c>
       <c r="D13" t="n">
-        <v>161.8044998013946</v>
+        <v>164.3610926233022</v>
       </c>
       <c r="E13" t="n">
-        <v>165.1500347889058</v>
+        <v>171.1120956061046</v>
       </c>
       <c r="F13" t="n">
-        <v>136975800</v>
+        <v>193114300</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45853</v>
+        <v>45861</v>
       </c>
       <c r="B14" t="n">
-        <v>170.4729461669922</v>
+        <v>170.5528411865234</v>
       </c>
       <c r="C14" t="n">
-        <v>172.1706819222518</v>
+        <v>171.0321984629863</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9749413408526</v>
+        <v>167.7465812569593</v>
       </c>
       <c r="E14" t="n">
-        <v>170.9622998960553</v>
+        <v>169.3045038343335</v>
       </c>
       <c r="F14" t="n">
-        <v>230627400</v>
+        <v>154082200</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45854</v>
+        <v>45862</v>
       </c>
       <c r="B15" t="n">
-        <v>171.1420593261719</v>
+        <v>173.5089263916016</v>
       </c>
       <c r="C15" t="n">
-        <v>171.5215587721167</v>
+        <v>173.5988030318276</v>
       </c>
       <c r="D15" t="n">
-        <v>168.6753434045181</v>
+        <v>171.0721692221773</v>
       </c>
       <c r="E15" t="n">
-        <v>170.832474089109</v>
+        <v>172.2106523805237</v>
       </c>
       <c r="F15" t="n">
-        <v>158831500</v>
+        <v>128984600</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45855</v>
+        <v>45863</v>
       </c>
       <c r="B16" t="n">
-        <v>172.7698974609375</v>
+        <v>173.2692413330078</v>
       </c>
       <c r="C16" t="n">
-        <v>173.9283582340991</v>
+        <v>174.4876199263022</v>
       </c>
       <c r="D16" t="n">
-        <v>170.6027855468386</v>
+        <v>172.7299662493585</v>
       </c>
       <c r="E16" t="n">
-        <v>171.7912051987463</v>
+        <v>173.3790956402227</v>
       </c>
       <c r="F16" t="n">
-        <v>160841100</v>
+        <v>122316800</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45856</v>
+        <v>45866</v>
       </c>
       <c r="B17" t="n">
-        <v>172.1806793212891</v>
+        <v>176.5149078369141</v>
       </c>
       <c r="C17" t="n">
-        <v>174.0182282608946</v>
+        <v>176.7645753161742</v>
       </c>
       <c r="D17" t="n">
-        <v>171.0321998051657</v>
+        <v>173.7386066866209</v>
       </c>
       <c r="E17" t="n">
-        <v>173.4090390187055</v>
+        <v>173.7885432301716</v>
       </c>
       <c r="F17" t="n">
-        <v>146456400</v>
+        <v>140023500</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45859</v>
+        <v>45867</v>
       </c>
       <c r="B18" t="n">
-        <v>171.1520690917969</v>
+        <v>175.2765350341797</v>
       </c>
       <c r="C18" t="n">
-        <v>173.1494090873095</v>
+        <v>179.1413976088354</v>
       </c>
       <c r="D18" t="n">
-        <v>170.7725696163311</v>
+        <v>174.7871965738649</v>
       </c>
       <c r="E18" t="n">
-        <v>172.5202421124047</v>
+        <v>177.7232882897224</v>
       </c>
       <c r="F18" t="n">
-        <v>123126100</v>
+        <v>154077500</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45860</v>
+        <v>45868</v>
       </c>
       <c r="B19" t="n">
-        <v>166.8078308105469</v>
+        <v>179.0315551757812</v>
       </c>
       <c r="C19" t="n">
-        <v>171.1620321483939</v>
+        <v>179.6507256303252</v>
       </c>
       <c r="D19" t="n">
-        <v>164.3610926233022</v>
+        <v>175.8058404642543</v>
       </c>
       <c r="E19" t="n">
-        <v>171.1120956061046</v>
+        <v>176.2752165309224</v>
       </c>
       <c r="F19" t="n">
-        <v>193114300</v>
+        <v>174312200</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45861</v>
+        <v>45869</v>
       </c>
       <c r="B20" t="n">
-        <v>170.5528411865234</v>
+        <v>177.6334228515625</v>
       </c>
       <c r="C20" t="n">
-        <v>171.0321984629863</v>
+        <v>183.0562087176856</v>
       </c>
       <c r="D20" t="n">
-        <v>167.7465812569593</v>
+        <v>175.6960006698149</v>
       </c>
       <c r="E20" t="n">
-        <v>169.3045038343335</v>
+        <v>182.6567315862202</v>
       </c>
       <c r="F20" t="n">
-        <v>154082200</v>
+        <v>221685400</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45862</v>
+        <v>45870</v>
       </c>
       <c r="B21" t="n">
-        <v>173.5089263916016</v>
+        <v>173.4889373779297</v>
       </c>
       <c r="C21" t="n">
-        <v>173.5988030318276</v>
+        <v>176.3051785902702</v>
       </c>
       <c r="D21" t="n">
-        <v>171.0721692221773</v>
+        <v>170.6626997138883</v>
       </c>
       <c r="E21" t="n">
-        <v>172.2106523805237</v>
+        <v>173.8584403670203</v>
       </c>
       <c r="F21" t="n">
-        <v>128984600</v>
+        <v>204529000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45863</v>
+        <v>45873</v>
       </c>
       <c r="B22" t="n">
-        <v>173.2692260742188</v>
+        <v>179.7605895996094</v>
       </c>
       <c r="C22" t="n">
-        <v>174.4876045602178</v>
+        <v>179.9603205403546</v>
       </c>
       <c r="D22" t="n">
-        <v>172.7299510380602</v>
+        <v>174.2878825830218</v>
       </c>
       <c r="E22" t="n">
-        <v>173.3790803717594</v>
+        <v>174.9270307365029</v>
       </c>
       <c r="F22" t="n">
-        <v>122316800</v>
+        <v>148174600</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45866</v>
+        <v>45874</v>
       </c>
       <c r="B23" t="n">
-        <v>176.5149078369141</v>
+        <v>178.0228881835938</v>
       </c>
       <c r="C23" t="n">
-        <v>176.7645753161742</v>
+        <v>180.0202279532499</v>
       </c>
       <c r="D23" t="n">
-        <v>173.7386066866209</v>
+        <v>175.6660266458598</v>
       </c>
       <c r="E23" t="n">
-        <v>173.7885432301716</v>
+        <v>179.3810798364997</v>
       </c>
       <c r="F23" t="n">
-        <v>140023500</v>
+        <v>156407600</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45867</v>
+        <v>45875</v>
       </c>
       <c r="B24" t="n">
-        <v>175.2765350341797</v>
+        <v>179.1813507080078</v>
       </c>
       <c r="C24" t="n">
-        <v>179.1413976088354</v>
+        <v>179.6607079907648</v>
       </c>
       <c r="D24" t="n">
-        <v>174.7871965738649</v>
+        <v>176.0155689699059</v>
       </c>
       <c r="E24" t="n">
-        <v>177.7232882897224</v>
+        <v>176.0954643901142</v>
       </c>
       <c r="F24" t="n">
-        <v>154077500</v>
+        <v>137192300</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45868</v>
+        <v>45876</v>
       </c>
       <c r="B25" t="n">
-        <v>179.0315704345703</v>
+        <v>180.5295562744141</v>
       </c>
       <c r="C25" t="n">
-        <v>179.6507409418859</v>
+        <v>183.6354201729052</v>
       </c>
       <c r="D25" t="n">
-        <v>175.8058554481169</v>
+        <v>178.5621754157094</v>
       </c>
       <c r="E25" t="n">
-        <v>176.2752315547899</v>
+        <v>181.3284952163767</v>
       </c>
       <c r="F25" t="n">
-        <v>174312200</v>
+        <v>151878400</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45869</v>
+        <v>45877</v>
       </c>
       <c r="B26" t="n">
-        <v>177.6334228515625</v>
+        <v>182.4569854736328</v>
       </c>
       <c r="C26" t="n">
-        <v>183.0562087176856</v>
+        <v>183.0561935017766</v>
       </c>
       <c r="D26" t="n">
-        <v>175.6960006698149</v>
+        <v>180.160041683739</v>
       </c>
       <c r="E26" t="n">
-        <v>182.6567315862202</v>
+        <v>181.3085211979325</v>
       </c>
       <c r="F26" t="n">
-        <v>221685400</v>
+        <v>123396700</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45870</v>
+        <v>45880</v>
       </c>
       <c r="B27" t="n">
-        <v>173.4889373779297</v>
+        <v>181.8178405761719</v>
       </c>
       <c r="C27" t="n">
-        <v>176.3051785902702</v>
+        <v>183.5954717890682</v>
       </c>
       <c r="D27" t="n">
-        <v>170.6626997138883</v>
+        <v>180.0102504851869</v>
       </c>
       <c r="E27" t="n">
-        <v>173.8584403670203</v>
+        <v>181.8078593629735</v>
       </c>
       <c r="F27" t="n">
-        <v>204529000</v>
+        <v>138323200</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45873</v>
+        <v>45881</v>
       </c>
       <c r="B28" t="n">
-        <v>179.7605743408203</v>
+        <v>182.9163818359375</v>
       </c>
       <c r="C28" t="n">
-        <v>179.9603052646116</v>
+        <v>184.234618174838</v>
       </c>
       <c r="D28" t="n">
-        <v>174.2878677887777</v>
+        <v>179.2213062678839</v>
       </c>
       <c r="E28" t="n">
-        <v>174.9270158880054</v>
+        <v>182.7166509044063</v>
       </c>
       <c r="F28" t="n">
-        <v>148174600</v>
+        <v>145485700</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45874</v>
+        <v>45882</v>
       </c>
       <c r="B29" t="n">
-        <v>178.0228881835938</v>
+        <v>181.3484649658203</v>
       </c>
       <c r="C29" t="n">
-        <v>180.0202279532499</v>
+        <v>183.7253042235627</v>
       </c>
       <c r="D29" t="n">
-        <v>175.6660266458598</v>
+        <v>179.1114541241742</v>
       </c>
       <c r="E29" t="n">
-        <v>179.3810798364997</v>
+        <v>182.3770937521473</v>
       </c>
       <c r="F29" t="n">
-        <v>156407600</v>
+        <v>179871700</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45875</v>
+        <v>45883</v>
       </c>
       <c r="B30" t="n">
-        <v>179.1813354492188</v>
+        <v>181.7778930664062</v>
       </c>
       <c r="C30" t="n">
-        <v>179.6606926911544</v>
+        <v>182.7765629312542</v>
       </c>
       <c r="D30" t="n">
-        <v>176.0155539807096</v>
+        <v>179.2213006505543</v>
       </c>
       <c r="E30" t="n">
-        <v>176.0954493941142</v>
+        <v>179.5109082064234</v>
       </c>
       <c r="F30" t="n">
-        <v>137192300</v>
+        <v>129554000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45876</v>
+        <v>45884</v>
       </c>
       <c r="B31" t="n">
-        <v>180.5295562744141</v>
+        <v>180.2099761962891</v>
       </c>
       <c r="C31" t="n">
-        <v>183.6354201729052</v>
+        <v>181.658044469753</v>
       </c>
       <c r="D31" t="n">
-        <v>178.5621754157094</v>
+        <v>177.8031781362909</v>
       </c>
       <c r="E31" t="n">
-        <v>181.3284952163767</v>
+        <v>181.6380820439347</v>
       </c>
       <c r="F31" t="n">
-        <v>151878400</v>
+        <v>156602200</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45877</v>
+        <v>45887</v>
       </c>
       <c r="B32" t="n">
-        <v>182.4569854736328</v>
+        <v>181.7678985595703</v>
       </c>
       <c r="C32" t="n">
-        <v>183.0561935017766</v>
+        <v>182.6966694678306</v>
       </c>
       <c r="D32" t="n">
-        <v>180.160041683739</v>
+        <v>180.3497891649352</v>
       </c>
       <c r="E32" t="n">
-        <v>181.3085211979325</v>
+        <v>180.359785616326</v>
       </c>
       <c r="F32" t="n">
-        <v>123396700</v>
+        <v>132008000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45880</v>
+        <v>45888</v>
       </c>
       <c r="B33" t="n">
-        <v>181.8178405761719</v>
+        <v>175.4063873291016</v>
       </c>
       <c r="C33" t="n">
-        <v>183.5954717890682</v>
+        <v>182.2572637144275</v>
       </c>
       <c r="D33" t="n">
-        <v>180.0102504851869</v>
+        <v>175.256592933775</v>
       </c>
       <c r="E33" t="n">
-        <v>181.8078593629735</v>
+        <v>182.1873495042791</v>
       </c>
       <c r="F33" t="n">
-        <v>138323200</v>
+        <v>185229200</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45881</v>
+        <v>45889</v>
       </c>
       <c r="B34" t="n">
-        <v>182.9163818359375</v>
+        <v>175.1667022705078</v>
       </c>
       <c r="C34" t="n">
-        <v>184.234618174838</v>
+        <v>175.7659103329496</v>
       </c>
       <c r="D34" t="n">
-        <v>179.2213062678839</v>
+        <v>168.5754897761186</v>
       </c>
       <c r="E34" t="n">
-        <v>182.7166509044063</v>
+        <v>174.9370124499192</v>
       </c>
       <c r="F34" t="n">
-        <v>145485700</v>
+        <v>215142700</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45882</v>
+        <v>45890</v>
       </c>
       <c r="B35" t="n">
-        <v>181.3484649658203</v>
+        <v>174.7472381591797</v>
       </c>
       <c r="C35" t="n">
-        <v>183.7253042235627</v>
+        <v>176.6646823555797</v>
       </c>
       <c r="D35" t="n">
-        <v>179.1114541241742</v>
+        <v>173.5787963163027</v>
       </c>
       <c r="E35" t="n">
-        <v>182.3770937521473</v>
+        <v>174.6174214467435</v>
       </c>
       <c r="F35" t="n">
-        <v>179871700</v>
+        <v>140040900</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45883</v>
+        <v>45891</v>
       </c>
       <c r="B36" t="n">
-        <v>181.7778930664062</v>
+        <v>177.7532501220703</v>
       </c>
       <c r="C36" t="n">
-        <v>182.7765629312542</v>
+        <v>178.3524428823499</v>
       </c>
       <c r="D36" t="n">
-        <v>179.2213006505543</v>
+        <v>170.9722733819868</v>
       </c>
       <c r="E36" t="n">
-        <v>179.5109082064234</v>
+        <v>172.3804015121563</v>
       </c>
       <c r="F36" t="n">
-        <v>129554000</v>
+        <v>172789400</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45884</v>
+        <v>45894</v>
       </c>
       <c r="B37" t="n">
-        <v>180.2099761962891</v>
+        <v>179.5708312988281</v>
       </c>
       <c r="C37" t="n">
-        <v>181.658044469753</v>
+        <v>181.6680441727565</v>
       </c>
       <c r="D37" t="n">
-        <v>177.8031781362909</v>
+        <v>176.3351505931587</v>
       </c>
       <c r="E37" t="n">
-        <v>181.6380820439347</v>
+        <v>178.112781786358</v>
       </c>
       <c r="F37" t="n">
-        <v>156602200</v>
+        <v>163012800</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45887</v>
+        <v>45895</v>
       </c>
       <c r="B38" t="n">
-        <v>181.7678985595703</v>
+        <v>181.5282287597656</v>
       </c>
       <c r="C38" t="n">
-        <v>182.6966694678306</v>
+        <v>182.1473992104306</v>
       </c>
       <c r="D38" t="n">
-        <v>180.3497891649352</v>
+        <v>178.5721592034272</v>
       </c>
       <c r="E38" t="n">
-        <v>180.359785616326</v>
+        <v>179.820496556215</v>
       </c>
       <c r="F38" t="n">
-        <v>132008000</v>
+        <v>168688200</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45888</v>
+        <v>45896</v>
       </c>
       <c r="B39" t="n">
-        <v>175.4063873291016</v>
+        <v>181.3584594726562</v>
       </c>
       <c r="C39" t="n">
-        <v>182.2572637144275</v>
+        <v>182.2472750718487</v>
       </c>
       <c r="D39" t="n">
-        <v>175.256592933775</v>
+        <v>178.8617847290266</v>
       </c>
       <c r="E39" t="n">
-        <v>182.1873495042791</v>
+        <v>181.7379436715125</v>
       </c>
       <c r="F39" t="n">
-        <v>185229200</v>
+        <v>235518900</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45889</v>
+        <v>45897</v>
       </c>
       <c r="B40" t="n">
-        <v>175.1667022705078</v>
+        <v>179.9303436279297</v>
       </c>
       <c r="C40" t="n">
-        <v>175.7659103329496</v>
+        <v>184.2246269967869</v>
       </c>
       <c r="D40" t="n">
-        <v>168.5754897761186</v>
+        <v>176.1753505073785</v>
       </c>
       <c r="E40" t="n">
-        <v>174.9370124499192</v>
+        <v>180.5794881684096</v>
       </c>
       <c r="F40" t="n">
-        <v>215142700</v>
+        <v>281787800</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45890</v>
+        <v>45898</v>
       </c>
       <c r="B41" t="n">
-        <v>174.7472381591797</v>
+        <v>173.9483032226562</v>
       </c>
       <c r="C41" t="n">
-        <v>176.6646823555797</v>
+        <v>177.9130236565273</v>
       </c>
       <c r="D41" t="n">
-        <v>173.5787963163027</v>
+        <v>172.9196745195101</v>
       </c>
       <c r="E41" t="n">
-        <v>174.6174214467435</v>
+        <v>177.8730835683677</v>
       </c>
       <c r="F41" t="n">
-        <v>140040900</v>
+        <v>243257900</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45891</v>
+        <v>45902</v>
       </c>
       <c r="B42" t="n">
-        <v>177.7532348632812</v>
+        <v>170.5528411865234</v>
       </c>
       <c r="C42" t="n">
-        <v>178.3524275721246</v>
+        <v>172.1507190927238</v>
       </c>
       <c r="D42" t="n">
-        <v>170.9722587052939</v>
+        <v>166.9975788456453</v>
       </c>
       <c r="E42" t="n">
-        <v>172.3803867145862</v>
+        <v>169.7738798978363</v>
       </c>
       <c r="F42" t="n">
-        <v>172789400</v>
+        <v>231164900</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45894</v>
+        <v>45903</v>
       </c>
       <c r="B43" t="n">
-        <v>179.5708465576172</v>
+        <v>170.3930511474609</v>
       </c>
       <c r="C43" t="n">
-        <v>181.6680596097534</v>
+        <v>172.1806787777383</v>
       </c>
       <c r="D43" t="n">
-        <v>176.3351655770002</v>
+        <v>168.6553752976972</v>
       </c>
       <c r="E43" t="n">
-        <v>178.1127969212513</v>
+        <v>170.8324683356518</v>
       </c>
       <c r="F43" t="n">
-        <v>163012800</v>
+        <v>164424900</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45895</v>
+        <v>45904</v>
       </c>
       <c r="B44" t="n">
-        <v>181.5282287597656</v>
+        <v>171.4316558837891</v>
       </c>
       <c r="C44" t="n">
-        <v>182.1473992104306</v>
+        <v>171.631386789518</v>
       </c>
       <c r="D44" t="n">
-        <v>178.5721592034272</v>
+        <v>169.1846489077332</v>
       </c>
       <c r="E44" t="n">
-        <v>179.820496556215</v>
+        <v>170.3431094948488</v>
       </c>
       <c r="F44" t="n">
-        <v>168688200</v>
+        <v>141670100</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45896</v>
+        <v>45905</v>
       </c>
       <c r="B45" t="n">
-        <v>181.3584594726562</v>
+        <v>166.7978515625</v>
       </c>
       <c r="C45" t="n">
-        <v>182.2472750718487</v>
+        <v>168.8051725828357</v>
       </c>
       <c r="D45" t="n">
-        <v>178.8617847290266</v>
+        <v>163.8517783946414</v>
       </c>
       <c r="E45" t="n">
-        <v>181.7379436715125</v>
+        <v>167.8065026792569</v>
       </c>
       <c r="F45" t="n">
-        <v>235518900</v>
+        <v>224441400</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45897</v>
+        <v>45908</v>
       </c>
       <c r="B46" t="n">
-        <v>179.9303436279297</v>
+        <v>168.0861358642578</v>
       </c>
       <c r="C46" t="n">
-        <v>184.2246269967869</v>
+        <v>170.7326203593915</v>
       </c>
       <c r="D46" t="n">
-        <v>176.1753505073785</v>
+        <v>167.127421251416</v>
       </c>
       <c r="E46" t="n">
-        <v>180.5794881684096</v>
+        <v>167.3271521925502</v>
       </c>
       <c r="F46" t="n">
-        <v>281787800</v>
+        <v>163769100</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45898</v>
+        <v>45909</v>
       </c>
       <c r="B47" t="n">
-        <v>173.9483032226562</v>
+        <v>170.5328674316406</v>
       </c>
       <c r="C47" t="n">
-        <v>177.9130236565273</v>
+        <v>170.7525760297424</v>
       </c>
       <c r="D47" t="n">
-        <v>172.9196745195101</v>
+        <v>166.5182253866755</v>
       </c>
       <c r="E47" t="n">
-        <v>177.8730835683677</v>
+        <v>168.8650905194996</v>
       </c>
       <c r="F47" t="n">
-        <v>243257900</v>
+        <v>157548400</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45902</v>
+        <v>45910</v>
       </c>
       <c r="B48" t="n">
-        <v>170.5528411865234</v>
+        <v>177.0941467285156</v>
       </c>
       <c r="C48" t="n">
-        <v>172.1507190927238</v>
+        <v>179.05153132643</v>
       </c>
       <c r="D48" t="n">
-        <v>166.9975788456453</v>
+        <v>175.2366199840082</v>
       </c>
       <c r="E48" t="n">
-        <v>169.7738798978363</v>
+        <v>176.4050620144814</v>
       </c>
       <c r="F48" t="n">
-        <v>231164900</v>
+        <v>226852000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45903</v>
+        <v>45911</v>
       </c>
       <c r="B49" t="n">
-        <v>170.39306640625</v>
+        <v>176.9443206787109</v>
       </c>
       <c r="C49" t="n">
-        <v>172.1806941966103</v>
+        <v>180.050359799309</v>
       </c>
       <c r="D49" t="n">
-        <v>168.6553904008765</v>
+        <v>176.2551971559751</v>
       </c>
       <c r="E49" t="n">
-        <v>170.832483633791</v>
+        <v>179.4511179779685</v>
       </c>
       <c r="F49" t="n">
-        <v>164424900</v>
+        <v>151159300</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45904</v>
+        <v>45912</v>
       </c>
       <c r="B50" t="n">
-        <v>171.4316864013672</v>
+        <v>177.5934906005859</v>
       </c>
       <c r="C50" t="n">
-        <v>171.6314173426514</v>
+        <v>178.3724957753353</v>
       </c>
       <c r="D50" t="n">
-        <v>169.1846790253082</v>
+        <v>176.2252254177762</v>
       </c>
       <c r="E50" t="n">
-        <v>170.3431398186483</v>
+        <v>177.5435512454145</v>
       </c>
       <c r="F50" t="n">
-        <v>141670100</v>
+        <v>124911000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45905</v>
+        <v>45915</v>
       </c>
       <c r="B51" t="n">
-        <v>166.7978363037109</v>
+        <v>177.5235900878906</v>
       </c>
       <c r="C51" t="n">
-        <v>168.8051571404154</v>
+        <v>178.6221950533741</v>
       </c>
       <c r="D51" t="n">
-        <v>163.8517634053613</v>
+        <v>174.28771156721</v>
       </c>
       <c r="E51" t="n">
-        <v>167.8064873281957</v>
+        <v>175.4462376691102</v>
       </c>
       <c r="F51" t="n">
-        <v>224441400</v>
+        <v>147061600</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45908</v>
+        <v>45916</v>
       </c>
       <c r="B52" t="n">
-        <v>168.0861358642578</v>
+        <v>174.6572570800781</v>
       </c>
       <c r="C52" t="n">
-        <v>170.7326203593915</v>
+        <v>177.2739150624347</v>
       </c>
       <c r="D52" t="n">
-        <v>167.127421251416</v>
+        <v>174.1578939390572</v>
       </c>
       <c r="E52" t="n">
-        <v>167.3271521925502</v>
+        <v>176.7745519214137</v>
       </c>
       <c r="F52" t="n">
-        <v>163769100</v>
+        <v>140737800</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45909</v>
+        <v>45917</v>
       </c>
       <c r="B53" t="n">
-        <v>170.5328674316406</v>
+        <v>170.0730743408203</v>
       </c>
       <c r="C53" t="n">
-        <v>170.7525760297424</v>
+        <v>172.9793711795688</v>
       </c>
       <c r="D53" t="n">
-        <v>166.5182253866755</v>
+        <v>168.1954794867923</v>
       </c>
       <c r="E53" t="n">
-        <v>168.8650905194996</v>
+        <v>172.4200869575455</v>
       </c>
       <c r="F53" t="n">
-        <v>157548400</v>
+        <v>211843800</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45910</v>
+        <v>45918</v>
       </c>
       <c r="B54" t="n">
-        <v>177.0941467285156</v>
+        <v>176.0155181884766</v>
       </c>
       <c r="C54" t="n">
-        <v>179.05153132643</v>
+        <v>176.8744233652544</v>
       </c>
       <c r="D54" t="n">
-        <v>175.2366199840082</v>
+        <v>172.7396973373594</v>
       </c>
       <c r="E54" t="n">
-        <v>176.4050620144814</v>
+        <v>173.7583871307785</v>
       </c>
       <c r="F54" t="n">
-        <v>226852000</v>
+        <v>191763300</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45911</v>
+        <v>45919</v>
       </c>
       <c r="B55" t="n">
-        <v>176.9443054199219</v>
+        <v>176.4449462890625</v>
       </c>
       <c r="C55" t="n">
-        <v>180.0503442726707</v>
+        <v>177.8531538116004</v>
       </c>
       <c r="D55" t="n">
-        <v>176.2551819566126</v>
+        <v>174.9568388461659</v>
       </c>
       <c r="E55" t="n">
-        <v>179.4511025030058</v>
+        <v>175.5460988538923</v>
       </c>
       <c r="F55" t="n">
-        <v>151159300</v>
+        <v>237182100</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45912</v>
+        <v>45922</v>
       </c>
       <c r="B56" t="n">
-        <v>177.593505859375</v>
+        <v>183.3761291503906</v>
       </c>
       <c r="C56" t="n">
-        <v>178.3725111010563</v>
+        <v>184.3149342727913</v>
       </c>
       <c r="D56" t="n">
-        <v>176.2252405590043</v>
+        <v>174.4874715349329</v>
       </c>
       <c r="E56" t="n">
-        <v>177.5435664999128</v>
+        <v>175.0767163707024</v>
       </c>
       <c r="F56" t="n">
-        <v>124911000</v>
+        <v>269637000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45915</v>
+        <v>45923</v>
       </c>
       <c r="B57" t="n">
-        <v>177.5235748291016</v>
+        <v>178.2027130126953</v>
       </c>
       <c r="C57" t="n">
-        <v>178.622179700156</v>
+        <v>182.187636136631</v>
       </c>
       <c r="D57" t="n">
-        <v>174.2876965865563</v>
+        <v>175.9855548133895</v>
       </c>
       <c r="E57" t="n">
-        <v>175.446222588877</v>
+        <v>181.7382123832494</v>
       </c>
       <c r="F57" t="n">
-        <v>147061600</v>
+        <v>192559600</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45916</v>
+        <v>45924</v>
       </c>
       <c r="B58" t="n">
-        <v>174.6572418212891</v>
+        <v>176.7445678710938</v>
       </c>
       <c r="C58" t="n">
-        <v>177.2738995750434</v>
+        <v>179.5509859124944</v>
       </c>
       <c r="D58" t="n">
-        <v>174.1578787238946</v>
+        <v>175.1765605017124</v>
       </c>
       <c r="E58" t="n">
-        <v>176.774536477649</v>
+        <v>179.5410041371674</v>
       </c>
       <c r="F58" t="n">
-        <v>140737800</v>
+        <v>143564100</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45917</v>
+        <v>45925</v>
       </c>
       <c r="B59" t="n">
-        <v>170.0730743408203</v>
+        <v>177.4636535644531</v>
       </c>
       <c r="C59" t="n">
-        <v>172.9793711795688</v>
+        <v>180.0303718676576</v>
       </c>
       <c r="D59" t="n">
-        <v>168.1954794867923</v>
+        <v>172.9094647194173</v>
       </c>
       <c r="E59" t="n">
-        <v>172.4200869575455</v>
+        <v>174.2577358899506</v>
       </c>
       <c r="F59" t="n">
-        <v>211843800</v>
+        <v>191586700</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45918</v>
+        <v>45926</v>
       </c>
       <c r="B60" t="n">
-        <v>176.0155181884766</v>
+        <v>177.9630279541016</v>
       </c>
       <c r="C60" t="n">
-        <v>176.8744233652544</v>
+        <v>179.5410172137402</v>
       </c>
       <c r="D60" t="n">
-        <v>172.7396973373594</v>
+        <v>174.7071707168733</v>
       </c>
       <c r="E60" t="n">
-        <v>173.7583871307785</v>
+        <v>177.9430491626408</v>
       </c>
       <c r="F60" t="n">
-        <v>191763300</v>
+        <v>148573700</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45919</v>
+        <v>45929</v>
       </c>
       <c r="B61" t="n">
-        <v>176.4449462890625</v>
+        <v>181.6183624267578</v>
       </c>
       <c r="C61" t="n">
-        <v>177.8531538116004</v>
+        <v>183.765617623905</v>
       </c>
       <c r="D61" t="n">
-        <v>174.9568388461659</v>
+        <v>180.0903125863159</v>
       </c>
       <c r="E61" t="n">
-        <v>175.5460988538923</v>
+        <v>180.2001578366391</v>
       </c>
       <c r="F61" t="n">
-        <v>237182100</v>
+        <v>193063500</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>45922</v>
+        <v>45930</v>
       </c>
       <c r="B62" t="n">
-        <v>183.3761291503906</v>
+        <v>186.3423309326172</v>
       </c>
       <c r="C62" t="n">
-        <v>184.3149342727913</v>
+        <v>187.1113543517957</v>
       </c>
       <c r="D62" t="n">
-        <v>174.4874715349329</v>
+        <v>181.2488213615314</v>
       </c>
       <c r="E62" t="n">
-        <v>175.0767163707024</v>
+        <v>181.848063160254</v>
       </c>
       <c r="F62" t="n">
-        <v>269637000</v>
+        <v>236981000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45923</v>
+        <v>45931</v>
       </c>
       <c r="B63" t="n">
-        <v>178.2027130126953</v>
+        <v>187.0015106201172</v>
       </c>
       <c r="C63" t="n">
-        <v>182.187636136631</v>
+        <v>187.9003581593927</v>
       </c>
       <c r="D63" t="n">
-        <v>175.9855548133895</v>
+        <v>183.665753326035</v>
       </c>
       <c r="E63" t="n">
-        <v>181.7382123832494</v>
+        <v>185.0040580978575</v>
       </c>
       <c r="F63" t="n">
-        <v>192559600</v>
+        <v>173844900</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45924</v>
+        <v>45932</v>
       </c>
       <c r="B64" t="n">
-        <v>176.7445678710938</v>
+        <v>188.6493988037109</v>
       </c>
       <c r="C64" t="n">
-        <v>179.5509859124944</v>
+        <v>190.806651138866</v>
       </c>
       <c r="D64" t="n">
-        <v>175.1765605017124</v>
+        <v>187.8204541960536</v>
       </c>
       <c r="E64" t="n">
-        <v>179.5410041371674</v>
+        <v>189.3585011391996</v>
       </c>
       <c r="F64" t="n">
-        <v>143564100</v>
+        <v>136805800</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>45925</v>
+        <v>45933</v>
       </c>
       <c r="B65" t="n">
-        <v>177.4636535644531</v>
+        <v>187.3810119628906</v>
       </c>
       <c r="C65" t="n">
-        <v>180.0303718676576</v>
+        <v>190.1175273421404</v>
       </c>
       <c r="D65" t="n">
-        <v>172.9094647194173</v>
+        <v>185.1438749421695</v>
       </c>
       <c r="E65" t="n">
-        <v>174.2577358899506</v>
+        <v>188.9490194719917</v>
       </c>
       <c r="F65" t="n">
-        <v>191586700</v>
+        <v>137596900</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>45926</v>
+        <v>45936</v>
       </c>
       <c r="B66" t="n">
-        <v>177.9630279541016</v>
+        <v>185.3036499023438</v>
       </c>
       <c r="C66" t="n">
-        <v>179.5410172137402</v>
+        <v>186.9914995955013</v>
       </c>
       <c r="D66" t="n">
-        <v>174.7071707168733</v>
+        <v>183.0964735646395</v>
       </c>
       <c r="E66" t="n">
-        <v>177.9430491626408</v>
+        <v>185.2637075602064</v>
       </c>
       <c r="F66" t="n">
-        <v>148573700</v>
+        <v>157678100</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>45929</v>
+        <v>45937</v>
       </c>
       <c r="B67" t="n">
-        <v>181.6183624267578</v>
+        <v>184.8043060302734</v>
       </c>
       <c r="C67" t="n">
-        <v>183.765617623905</v>
+        <v>188.8191899838309</v>
       </c>
       <c r="D67" t="n">
-        <v>180.0903125863159</v>
+        <v>183.7656373937981</v>
       </c>
       <c r="E67" t="n">
-        <v>180.2001578366391</v>
+        <v>185.9927927538886</v>
       </c>
       <c r="F67" t="n">
-        <v>193063500</v>
+        <v>140088000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>45930</v>
+        <v>45938</v>
       </c>
       <c r="B68" t="n">
-        <v>186.3423309326172</v>
+        <v>188.8691101074219</v>
       </c>
       <c r="C68" t="n">
-        <v>187.1113543517957</v>
+        <v>189.3584914259294</v>
       </c>
       <c r="D68" t="n">
-        <v>181.2488213615314</v>
+        <v>186.3023764882154</v>
       </c>
       <c r="E68" t="n">
-        <v>181.848063160254</v>
+        <v>186.3323522940729</v>
       </c>
       <c r="F68" t="n">
-        <v>236981000</v>
+        <v>130168900</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>45931</v>
+        <v>45939</v>
       </c>
       <c r="B69" t="n">
-        <v>187.0015106201172</v>
+        <v>192.32470703125</v>
       </c>
       <c r="C69" t="n">
-        <v>187.9003581593927</v>
+        <v>195.0512252247687</v>
       </c>
       <c r="D69" t="n">
-        <v>183.665753326035</v>
+        <v>190.816620752273</v>
       </c>
       <c r="E69" t="n">
-        <v>185.0040580978575</v>
+        <v>191.9851285494953</v>
       </c>
       <c r="F69" t="n">
-        <v>173844900</v>
+        <v>182997200</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>45932</v>
+        <v>45940</v>
       </c>
       <c r="B70" t="n">
-        <v>188.6493988037109</v>
+        <v>182.9266967773438</v>
       </c>
       <c r="C70" t="n">
-        <v>190.806651138866</v>
+        <v>195.3708168536685</v>
       </c>
       <c r="D70" t="n">
-        <v>187.8204541960536</v>
+        <v>181.8181100716619</v>
       </c>
       <c r="E70" t="n">
-        <v>189.3585011391996</v>
+        <v>193.263503935277</v>
       </c>
       <c r="F70" t="n">
-        <v>136805800</v>
+        <v>268774400</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>45933</v>
+        <v>45943</v>
       </c>
       <c r="B71" t="n">
-        <v>187.3809967041016</v>
+        <v>188.0801239013672</v>
       </c>
       <c r="C71" t="n">
-        <v>190.1175118605118</v>
+        <v>189.8678370807686</v>
       </c>
       <c r="D71" t="n">
-        <v>185.1438598655547</v>
+        <v>185.7231294773067</v>
       </c>
       <c r="E71" t="n">
-        <v>188.9490040855168</v>
+        <v>187.7305636382236</v>
       </c>
       <c r="F71" t="n">
-        <v>137596900</v>
+        <v>153482800</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>45936</v>
+        <v>45944</v>
       </c>
       <c r="B72" t="n">
-        <v>185.3036651611328</v>
+        <v>179.8006744384766</v>
       </c>
       <c r="C72" t="n">
-        <v>186.991514993276</v>
+        <v>184.5646026231026</v>
       </c>
       <c r="D72" t="n">
-        <v>183.0964886416791</v>
+        <v>179.4710929676557</v>
       </c>
       <c r="E72" t="n">
-        <v>185.2637228157064</v>
+        <v>184.5346420566055</v>
       </c>
       <c r="F72" t="n">
-        <v>157678100</v>
+        <v>205641400</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>45937</v>
+        <v>45945</v>
       </c>
       <c r="B73" t="n">
-        <v>184.8042907714844</v>
+        <v>179.6009368896484</v>
       </c>
       <c r="C73" t="n">
-        <v>188.8191743935438</v>
+        <v>184.6345103028178</v>
       </c>
       <c r="D73" t="n">
-        <v>183.765622220769</v>
+        <v>177.064163772089</v>
       </c>
       <c r="E73" t="n">
-        <v>185.9927773969694</v>
+        <v>184.5646073923022</v>
       </c>
       <c r="F73" t="n">
-        <v>140088000</v>
+        <v>214450500</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>45938</v>
+        <v>45946</v>
       </c>
       <c r="B74" t="n">
-        <v>188.8691101074219</v>
+        <v>181.5783996582031</v>
       </c>
       <c r="C74" t="n">
-        <v>189.3584914259294</v>
+        <v>183.0465283240366</v>
       </c>
       <c r="D74" t="n">
-        <v>186.3023764882154</v>
+        <v>179.5410050089342</v>
       </c>
       <c r="E74" t="n">
-        <v>186.3323522940729</v>
+        <v>181.9978628142482</v>
       </c>
       <c r="F74" t="n">
-        <v>130168900</v>
+        <v>179723300</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>45939</v>
+        <v>45947</v>
       </c>
       <c r="B75" t="n">
-        <v>192.32470703125</v>
+        <v>182.9866027832031</v>
       </c>
       <c r="C75" t="n">
-        <v>195.0512252247687</v>
+        <v>183.8654866543178</v>
       </c>
       <c r="D75" t="n">
-        <v>190.816620752273</v>
+        <v>179.5210218924729</v>
       </c>
       <c r="E75" t="n">
-        <v>191.9851285494953</v>
+        <v>179.950466813544</v>
       </c>
       <c r="F75" t="n">
-        <v>182997200</v>
+        <v>173135200</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>45940</v>
+        <v>45950</v>
       </c>
       <c r="B76" t="n">
-        <v>182.9266967773438</v>
+        <v>182.4073486328125</v>
       </c>
       <c r="C76" t="n">
-        <v>195.3708168536685</v>
+        <v>184.9640852114922</v>
       </c>
       <c r="D76" t="n">
-        <v>181.8181100716619</v>
+        <v>181.4985041529273</v>
       </c>
       <c r="E76" t="n">
-        <v>193.263503935277</v>
+        <v>182.8967299464473</v>
       </c>
       <c r="F76" t="n">
-        <v>268774400</v>
+        <v>128544700</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>45943</v>
+        <v>45951</v>
       </c>
       <c r="B77" t="n">
-        <v>188.0801391601562</v>
+        <v>180.9292449951172</v>
       </c>
       <c r="C77" t="n">
-        <v>189.8678524845934</v>
+        <v>182.5571583648613</v>
       </c>
       <c r="D77" t="n">
-        <v>185.7231445448746</v>
+        <v>179.5709767314294</v>
       </c>
       <c r="E77" t="n">
-        <v>187.7305788686531</v>
+        <v>182.5571583648613</v>
       </c>
       <c r="F77" t="n">
-        <v>153482800</v>
+        <v>124240200</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>45944</v>
+        <v>45952</v>
       </c>
       <c r="B78" t="n">
-        <v>179.8006744384766</v>
+        <v>180.0503692626953</v>
       </c>
       <c r="C78" t="n">
-        <v>184.5646026231026</v>
+        <v>183.2063479075077</v>
       </c>
       <c r="D78" t="n">
-        <v>179.4710929676557</v>
+        <v>176.5348485540517</v>
       </c>
       <c r="E78" t="n">
-        <v>184.5346420566055</v>
+        <v>180.9092744574391</v>
       </c>
       <c r="F78" t="n">
-        <v>205641400</v>
+        <v>162249600</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>45945</v>
+        <v>45953</v>
       </c>
       <c r="B79" t="n">
-        <v>179.6009368896484</v>
+        <v>181.9279632568359</v>
       </c>
       <c r="C79" t="n">
-        <v>184.6345103028178</v>
+        <v>182.7968501503985</v>
       </c>
       <c r="D79" t="n">
-        <v>177.064163772089</v>
+        <v>179.5609718650331</v>
       </c>
       <c r="E79" t="n">
-        <v>184.5646073923022</v>
+        <v>180.1901742303588</v>
       </c>
       <c r="F79" t="n">
-        <v>214450500</v>
+        <v>111363700</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>45946</v>
+        <v>45954</v>
       </c>
       <c r="B80" t="n">
-        <v>181.5783996582031</v>
+        <v>186.0227203369141</v>
       </c>
       <c r="C80" t="n">
-        <v>183.0465283240366</v>
+        <v>187.2311856390606</v>
       </c>
       <c r="D80" t="n">
-        <v>179.5410050089342</v>
+        <v>183.2662417509678</v>
       </c>
       <c r="E80" t="n">
-        <v>181.9978628142482</v>
+        <v>183.6058049719722</v>
       </c>
       <c r="F80" t="n">
-        <v>179723300</v>
+        <v>131296700</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>45947</v>
+        <v>45957</v>
       </c>
       <c r="B81" t="n">
-        <v>182.9866180419922</v>
+        <v>191.2460784912109</v>
       </c>
       <c r="C81" t="n">
-        <v>183.8655019863948</v>
+        <v>191.7554233483132</v>
       </c>
       <c r="D81" t="n">
-        <v>179.521036862276</v>
+        <v>188.1899636305417</v>
       </c>
       <c r="E81" t="n">
-        <v>179.9504818191574</v>
+        <v>189.7479892463022</v>
       </c>
       <c r="F81" t="n">
-        <v>173135200</v>
+        <v>153452700</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>45950</v>
+        <v>45958</v>
       </c>
       <c r="B82" t="n">
-        <v>182.4073486328125</v>
+        <v>200.77392578125</v>
       </c>
       <c r="C82" t="n">
-        <v>184.9640852114922</v>
+        <v>202.8912204382634</v>
       </c>
       <c r="D82" t="n">
-        <v>181.4985041529273</v>
+        <v>191.6655477585559</v>
       </c>
       <c r="E82" t="n">
-        <v>182.8967299464473</v>
+        <v>192.8040950113927</v>
       </c>
       <c r="F82" t="n">
-        <v>128544700</v>
+        <v>297986200</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>45951</v>
+        <v>45959</v>
       </c>
       <c r="B83" t="n">
-        <v>180.9292449951172</v>
+        <v>206.7762756347656</v>
       </c>
       <c r="C83" t="n">
-        <v>182.5571583648613</v>
+        <v>211.9197249544373</v>
       </c>
       <c r="D83" t="n">
-        <v>179.5709767314294</v>
+        <v>204.5191598009531</v>
       </c>
       <c r="E83" t="n">
-        <v>182.5571583648613</v>
+        <v>207.715080745974</v>
       </c>
       <c r="F83" t="n">
-        <v>124240200</v>
+        <v>308829600</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>45952</v>
+        <v>45960</v>
       </c>
       <c r="B84" t="n">
-        <v>180.0503540039062</v>
+        <v>202.6315612792969</v>
       </c>
       <c r="C84" t="n">
-        <v>183.2063323812579</v>
+        <v>205.8974002714209</v>
       </c>
       <c r="D84" t="n">
-        <v>176.5348335931937</v>
+        <v>201.1534507471854</v>
       </c>
       <c r="E84" t="n">
-        <v>180.9092591258601</v>
+        <v>204.8886770404504</v>
       </c>
       <c r="F84" t="n">
-        <v>162249600</v>
+        <v>178864400</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>45953</v>
+        <v>45961</v>
       </c>
       <c r="B85" t="n">
-        <v>181.9279632568359</v>
+        <v>202.2320709228516</v>
       </c>
       <c r="C85" t="n">
-        <v>182.7968501503985</v>
+        <v>207.7050861560208</v>
       </c>
       <c r="D85" t="n">
-        <v>179.5609718650331</v>
+        <v>201.8126077533842</v>
       </c>
       <c r="E85" t="n">
-        <v>180.1901742303588</v>
+        <v>206.1870180860303</v>
       </c>
       <c r="F85" t="n">
-        <v>111363700</v>
+        <v>179802200</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>45954</v>
+        <v>45964</v>
       </c>
       <c r="B86" t="n">
-        <v>186.0227355957031</v>
+        <v>206.6164703369141</v>
       </c>
       <c r="C86" t="n">
-        <v>187.2312009969758</v>
+        <v>211.0707804221397</v>
       </c>
       <c r="D86" t="n">
-        <v>183.2662567836526</v>
+        <v>205.2981445069072</v>
       </c>
       <c r="E86" t="n">
-        <v>183.6058200325102</v>
+        <v>207.8149386664238</v>
       </c>
       <c r="F86" t="n">
-        <v>131296700</v>
+        <v>180267300</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>45957</v>
+        <v>45965</v>
       </c>
       <c r="B87" t="n">
-        <v>191.24609375</v>
+        <v>198.4369049072266</v>
       </c>
       <c r="C87" t="n">
-        <v>191.755438647741</v>
+        <v>203.7101778590782</v>
       </c>
       <c r="D87" t="n">
-        <v>188.189978645495</v>
+        <v>197.6778632657914</v>
       </c>
       <c r="E87" t="n">
-        <v>189.7480043855645</v>
+        <v>202.7414122562426</v>
       </c>
       <c r="F87" t="n">
-        <v>153452700</v>
+        <v>188919300</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>45958</v>
+        <v>45966</v>
       </c>
       <c r="B88" t="n">
-        <v>200.77392578125</v>
+        <v>194.9613647460938</v>
       </c>
       <c r="C88" t="n">
-        <v>202.8912204382634</v>
+        <v>202.6615358672701</v>
       </c>
       <c r="D88" t="n">
-        <v>191.6655477585559</v>
+        <v>194.4020652255917</v>
       </c>
       <c r="E88" t="n">
-        <v>192.8040950113927</v>
+        <v>198.5168278814111</v>
       </c>
       <c r="F88" t="n">
-        <v>297986200</v>
+        <v>171350300</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>45959</v>
+        <v>45967</v>
       </c>
       <c r="B89" t="n">
-        <v>206.7762756347656</v>
+        <v>187.8404388427734</v>
       </c>
       <c r="C89" t="n">
-        <v>211.9197249544373</v>
+        <v>197.3682807609907</v>
       </c>
       <c r="D89" t="n">
-        <v>204.5191598009531</v>
+        <v>186.1426072302662</v>
       </c>
       <c r="E89" t="n">
-        <v>207.715080745974</v>
+        <v>196.1698122838887</v>
       </c>
       <c r="F89" t="n">
-        <v>308829600</v>
+        <v>223029800</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>45960</v>
+        <v>45968</v>
       </c>
       <c r="B90" t="n">
-        <v>202.6315612792969</v>
+        <v>187.9103240966797</v>
       </c>
       <c r="C90" t="n">
-        <v>205.8974002714209</v>
+        <v>188.0801209573904</v>
       </c>
       <c r="D90" t="n">
-        <v>201.1534507471854</v>
+        <v>178.6821039748825</v>
       </c>
       <c r="E90" t="n">
-        <v>204.8886770404504</v>
+        <v>184.6644640216047</v>
       </c>
       <c r="F90" t="n">
-        <v>178864400</v>
+        <v>264942300</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>45961</v>
+        <v>45971</v>
       </c>
       <c r="B91" t="n">
-        <v>202.2320709228516</v>
+        <v>198.7964630126953</v>
       </c>
       <c r="C91" t="n">
-        <v>207.7050861560208</v>
+        <v>199.6853287651845</v>
       </c>
       <c r="D91" t="n">
-        <v>201.8126077533842</v>
+        <v>193.5431531870904</v>
       </c>
       <c r="E91" t="n">
-        <v>206.1870180860303</v>
+        <v>194.8614791513322</v>
       </c>
       <c r="F91" t="n">
-        <v>179802200</v>
+        <v>198897100</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>45964</v>
+        <v>45972</v>
       </c>
       <c r="B92" t="n">
-        <v>206.6164855957031</v>
+        <v>192.9139556884766</v>
       </c>
       <c r="C92" t="n">
-        <v>211.0707960098831</v>
+        <v>195.1710714054063</v>
       </c>
       <c r="D92" t="n">
-        <v>205.2981596683369</v>
+        <v>191.0563243542301</v>
       </c>
       <c r="E92" t="n">
-        <v>207.8149540137207</v>
+        <v>194.9114080805974</v>
       </c>
       <c r="F92" t="n">
-        <v>180267300</v>
+        <v>176483300</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>45965</v>
+        <v>45973</v>
       </c>
       <c r="B93" t="n">
-        <v>198.4369049072266</v>
+        <v>193.5531463623047</v>
       </c>
       <c r="C93" t="n">
-        <v>203.7101778590782</v>
+        <v>195.6404805249176</v>
       </c>
       <c r="D93" t="n">
-        <v>197.6778632657914</v>
+        <v>190.8865491577477</v>
       </c>
       <c r="E93" t="n">
-        <v>202.7414122562426</v>
+        <v>195.4706988945922</v>
       </c>
       <c r="F93" t="n">
-        <v>188919300</v>
+        <v>154935300</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>45966</v>
+        <v>45974</v>
       </c>
       <c r="B94" t="n">
-        <v>194.9613494873047</v>
+        <v>186.6219787597656</v>
       </c>
       <c r="C94" t="n">
-        <v>202.6615200058216</v>
+        <v>191.1961465947379</v>
       </c>
       <c r="D94" t="n">
-        <v>194.4020500105767</v>
+        <v>183.6158183771961</v>
       </c>
       <c r="E94" t="n">
-        <v>198.5168123443512</v>
+        <v>190.8066439854392</v>
       </c>
       <c r="F94" t="n">
-        <v>171350300</v>
+        <v>207423100</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>45967</v>
+        <v>45975</v>
       </c>
       <c r="B95" t="n">
-        <v>187.8404388427734</v>
+        <v>189.9277496337891</v>
       </c>
       <c r="C95" t="n">
-        <v>197.3682807609907</v>
+        <v>190.7666759402113</v>
       </c>
       <c r="D95" t="n">
-        <v>186.1426072302662</v>
+        <v>180.3499695370899</v>
       </c>
       <c r="E95" t="n">
-        <v>196.1698122838887</v>
+        <v>182.6270639341511</v>
       </c>
       <c r="F95" t="n">
-        <v>223029800</v>
+        <v>186591900</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>45968</v>
+        <v>45978</v>
       </c>
       <c r="B96" t="n">
-        <v>187.9103088378906</v>
+        <v>186.3623199462891</v>
       </c>
       <c r="C96" t="n">
-        <v>188.0801056848134</v>
+        <v>188.7592567939633</v>
       </c>
       <c r="D96" t="n">
-        <v>178.682089465448</v>
+        <v>184.0852253691927</v>
       </c>
       <c r="E96" t="n">
-        <v>184.6644490263876</v>
+        <v>185.7331175470496</v>
       </c>
       <c r="F96" t="n">
-        <v>264942300</v>
+        <v>173628900</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>45971</v>
+        <v>45979</v>
       </c>
       <c r="B97" t="n">
-        <v>198.7964630126953</v>
+        <v>181.1289825439453</v>
       </c>
       <c r="C97" t="n">
-        <v>199.6853287651845</v>
+        <v>184.5646030780414</v>
       </c>
       <c r="D97" t="n">
-        <v>193.5431531870904</v>
+        <v>179.4211540526368</v>
       </c>
       <c r="E97" t="n">
-        <v>194.8614791513322</v>
+        <v>183.1464137160556</v>
       </c>
       <c r="F97" t="n">
-        <v>198897100</v>
+        <v>213598900</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>45972</v>
+        <v>45980</v>
       </c>
       <c r="B98" t="n">
-        <v>192.9139556884766</v>
+        <v>186.2824096679688</v>
       </c>
       <c r="C98" t="n">
-        <v>195.1710714054063</v>
+        <v>187.6206990795639</v>
       </c>
       <c r="D98" t="n">
-        <v>191.0563243542301</v>
+        <v>182.5971076589588</v>
       </c>
       <c r="E98" t="n">
-        <v>194.9114080805974</v>
+        <v>184.5546024199349</v>
       </c>
       <c r="F98" t="n">
-        <v>176483300</v>
+        <v>247246400</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>45973</v>
+        <v>45981</v>
       </c>
       <c r="B99" t="n">
-        <v>193.5531311035156</v>
+        <v>180.4098968505859</v>
       </c>
       <c r="C99" t="n">
-        <v>195.6404651015733</v>
+        <v>195.7503316108911</v>
       </c>
       <c r="D99" t="n">
-        <v>190.8865341091802</v>
+        <v>179.6209098723672</v>
       </c>
       <c r="E99" t="n">
-        <v>195.4706834846326</v>
+        <v>195.7003922539362</v>
       </c>
       <c r="F99" t="n">
-        <v>154935300</v>
+        <v>343504800</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>45974</v>
+        <v>45982</v>
       </c>
       <c r="B100" t="n">
-        <v>186.6219787597656</v>
+        <v>178.6521453857422</v>
       </c>
       <c r="C100" t="n">
-        <v>191.1961465947379</v>
+        <v>184.3249028186839</v>
       </c>
       <c r="D100" t="n">
-        <v>183.6158183771961</v>
+        <v>172.7097123756701</v>
       </c>
       <c r="E100" t="n">
-        <v>190.8066439854392</v>
+        <v>181.0091397989924</v>
       </c>
       <c r="F100" t="n">
-        <v>207423100</v>
+        <v>346926200</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>45975</v>
+        <v>45985</v>
       </c>
       <c r="B101" t="n">
-        <v>189.9277496337891</v>
+        <v>182.3174743652344</v>
       </c>
       <c r="C101" t="n">
-        <v>190.7666759402113</v>
+        <v>183.2662612256163</v>
       </c>
       <c r="D101" t="n">
-        <v>180.3499695370899</v>
+        <v>176.2551988997211</v>
       </c>
       <c r="E101" t="n">
-        <v>182.6270639341511</v>
+        <v>179.2613745727385</v>
       </c>
       <c r="F101" t="n">
-        <v>186591900</v>
+        <v>256618300</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>45978</v>
+        <v>45986</v>
       </c>
       <c r="B102" t="n">
-        <v>186.3623199462891</v>
+        <v>177.5934906005859</v>
       </c>
       <c r="C102" t="n">
-        <v>188.7592567939633</v>
+        <v>177.9330538327892</v>
       </c>
       <c r="D102" t="n">
-        <v>184.0852253691927</v>
+        <v>169.3340211059625</v>
       </c>
       <c r="E102" t="n">
-        <v>185.7331175470496</v>
+        <v>174.6871938582165</v>
       </c>
       <c r="F102" t="n">
-        <v>173628900</v>
+        <v>320600300</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>45979</v>
+        <v>45987</v>
       </c>
       <c r="B103" t="n">
-        <v>181.1289825439453</v>
+        <v>180.0303802490234</v>
       </c>
       <c r="C103" t="n">
-        <v>184.5646030780414</v>
+        <v>182.6770138362068</v>
       </c>
       <c r="D103" t="n">
-        <v>179.4211540526368</v>
+        <v>178.0129642870119</v>
       </c>
       <c r="E103" t="n">
-        <v>183.1464137160556</v>
+        <v>181.3986455127995</v>
       </c>
       <c r="F103" t="n">
-        <v>213598900</v>
+        <v>183852000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>45980</v>
+        <v>45989</v>
       </c>
       <c r="B104" t="n">
-        <v>186.2824096679688</v>
+        <v>176.7745361328125</v>
       </c>
       <c r="C104" t="n">
-        <v>187.6206990795639</v>
+        <v>179.0616124091028</v>
       </c>
       <c r="D104" t="n">
-        <v>182.5971076589588</v>
+        <v>176.2751730363921</v>
       </c>
       <c r="E104" t="n">
-        <v>184.5546024199349</v>
+        <v>178.7819702942556</v>
       </c>
       <c r="F104" t="n">
-        <v>247246400</v>
+        <v>121332800</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>45981</v>
+        <v>45992</v>
       </c>
       <c r="B105" t="n">
-        <v>180.4098968505859</v>
+        <v>179.6908111572266</v>
       </c>
       <c r="C105" t="n">
-        <v>195.7503316108911</v>
+        <v>180.070331979432</v>
       </c>
       <c r="D105" t="n">
-        <v>179.6209098723672</v>
+        <v>173.4587543536281</v>
       </c>
       <c r="E105" t="n">
-        <v>195.7003922539362</v>
+        <v>174.5373804488289</v>
       </c>
       <c r="F105" t="n">
-        <v>343504800</v>
+        <v>188131000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>45982</v>
+        <v>45993</v>
       </c>
       <c r="B106" t="n">
-        <v>178.6521453857422</v>
+        <v>181.2288665771484</v>
       </c>
       <c r="C106" t="n">
-        <v>184.3249028186839</v>
+        <v>185.4235136530611</v>
       </c>
       <c r="D106" t="n">
-        <v>172.7097123756701</v>
+        <v>179.7707195907086</v>
       </c>
       <c r="E106" t="n">
-        <v>181.0091397989924</v>
+        <v>181.5284722516508</v>
       </c>
       <c r="F106" t="n">
-        <v>346926200</v>
+        <v>182632200</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>45985</v>
+        <v>45994</v>
       </c>
       <c r="B107" t="n">
-        <v>182.3174743652344</v>
+        <v>179.3612365722656</v>
       </c>
       <c r="C107" t="n">
-        <v>183.2662612256163</v>
+        <v>182.2175941452395</v>
       </c>
       <c r="D107" t="n">
-        <v>176.2551988997211</v>
+        <v>178.8818522580144</v>
       </c>
       <c r="E107" t="n">
-        <v>179.2613745727385</v>
+        <v>180.8493441127912</v>
       </c>
       <c r="F107" t="n">
-        <v>256618300</v>
+        <v>165138000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>45986</v>
+        <v>45995</v>
       </c>
       <c r="B108" t="n">
-        <v>177.593505859375</v>
+        <v>183.1566162109375</v>
       </c>
       <c r="C108" t="n">
-        <v>177.9330691207534</v>
+        <v>184.2952268834804</v>
       </c>
       <c r="D108" t="n">
-        <v>169.3340356551</v>
+        <v>179.7407841933088</v>
       </c>
       <c r="E108" t="n">
-        <v>174.6872088672972</v>
+        <v>181.3987504426599</v>
       </c>
       <c r="F108" t="n">
-        <v>320600300</v>
+        <v>167364900</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>45987</v>
+        <v>45996</v>
       </c>
       <c r="B109" t="n">
-        <v>180.0303649902344</v>
+        <v>182.1877899169922</v>
       </c>
       <c r="C109" t="n">
-        <v>182.6769983530976</v>
+        <v>184.4350489438193</v>
       </c>
       <c r="D109" t="n">
-        <v>178.0129491992125</v>
+        <v>180.6896172324408</v>
       </c>
       <c r="E109" t="n">
-        <v>181.3986301380407</v>
+        <v>183.6659826984934</v>
       </c>
       <c r="F109" t="n">
-        <v>183852000</v>
+        <v>143971100</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>45989</v>
+        <v>45999</v>
       </c>
       <c r="B110" t="n">
-        <v>176.7745361328125</v>
+        <v>185.323974609375</v>
       </c>
       <c r="C110" t="n">
-        <v>179.0616124091028</v>
+        <v>187.7709870845105</v>
       </c>
       <c r="D110" t="n">
-        <v>176.2751730363921</v>
+        <v>182.1778026497423</v>
       </c>
       <c r="E110" t="n">
-        <v>178.7819702942556</v>
+        <v>182.4175157793015</v>
       </c>
       <c r="F110" t="n">
-        <v>121332800</v>
+        <v>204378100</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>45992</v>
+        <v>46000</v>
       </c>
       <c r="B111" t="n">
-        <v>179.6908111572266</v>
+        <v>184.7446746826172</v>
       </c>
       <c r="C111" t="n">
-        <v>180.070331979432</v>
+        <v>185.4937610485011</v>
       </c>
       <c r="D111" t="n">
-        <v>173.4587543536281</v>
+        <v>183.096690773753</v>
       </c>
       <c r="E111" t="n">
-        <v>174.5373804488289</v>
+        <v>185.3339522994643</v>
       </c>
       <c r="F111" t="n">
-        <v>188131000</v>
+        <v>144719700</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>45993</v>
+        <v>46001</v>
       </c>
       <c r="B112" t="n">
-        <v>181.2288665771484</v>
+        <v>183.5561218261719</v>
       </c>
       <c r="C112" t="n">
-        <v>185.4235136530611</v>
+        <v>185.2540478736652</v>
       </c>
       <c r="D112" t="n">
-        <v>179.7707195907086</v>
+        <v>181.8182359713298</v>
       </c>
       <c r="E112" t="n">
-        <v>181.5284722516508</v>
+        <v>184.7446746314776</v>
       </c>
       <c r="F112" t="n">
-        <v>182632200</v>
+        <v>162785400</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>45994</v>
+        <v>46002</v>
       </c>
       <c r="B113" t="n">
-        <v>179.3612518310547</v>
+        <v>180.7095794677734</v>
       </c>
       <c r="C113" t="n">
-        <v>182.2176096470274</v>
+        <v>181.0991189911166</v>
       </c>
       <c r="D113" t="n">
-        <v>178.8818674760209</v>
+        <v>176.4048324504213</v>
       </c>
       <c r="E113" t="n">
-        <v>180.849359498178</v>
+        <v>180.060377409269</v>
       </c>
       <c r="F113" t="n">
-        <v>165138000</v>
+        <v>182136600</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>45995</v>
+        <v>46003</v>
       </c>
       <c r="B114" t="n">
-        <v>183.1566009521484</v>
+        <v>174.8067932128906</v>
       </c>
       <c r="C114" t="n">
-        <v>184.2952115298336</v>
+        <v>182.5972942255974</v>
       </c>
       <c r="D114" t="n">
-        <v>179.7407692190929</v>
+        <v>174.4072713526335</v>
       </c>
       <c r="E114" t="n">
-        <v>181.3987353303187</v>
+        <v>180.8893706584245</v>
       </c>
       <c r="F114" t="n">
-        <v>167364900</v>
+        <v>204274900</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>45996</v>
+        <v>46006</v>
       </c>
       <c r="B115" t="n">
-        <v>182.1877899169922</v>
+        <v>176.0752410888672</v>
       </c>
       <c r="C115" t="n">
-        <v>184.4350489438193</v>
+        <v>178.2026512513541</v>
       </c>
       <c r="D115" t="n">
-        <v>180.6896172324408</v>
+        <v>174.8167814768023</v>
       </c>
       <c r="E115" t="n">
-        <v>183.6659826984934</v>
+        <v>177.7232402429772</v>
       </c>
       <c r="F115" t="n">
-        <v>143971100</v>
+        <v>164775600</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>45999</v>
+        <v>46007</v>
       </c>
       <c r="B116" t="n">
-        <v>185.323974609375</v>
+        <v>177.5035095214844</v>
       </c>
       <c r="C116" t="n">
-        <v>187.7709870845105</v>
+        <v>178.27257580423</v>
       </c>
       <c r="D116" t="n">
-        <v>182.1778026497423</v>
+        <v>174.6869374221882</v>
       </c>
       <c r="E116" t="n">
-        <v>182.4175157793015</v>
+        <v>176.0452813318811</v>
       </c>
       <c r="F116" t="n">
-        <v>204378100</v>
+        <v>148588100</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>46000</v>
+        <v>46008</v>
       </c>
       <c r="B117" t="n">
-        <v>184.7446746826172</v>
+        <v>170.7317657470703</v>
       </c>
       <c r="C117" t="n">
-        <v>185.4937610485011</v>
+        <v>175.9154458008753</v>
       </c>
       <c r="D117" t="n">
-        <v>183.096690773753</v>
+        <v>170.1025283272995</v>
       </c>
       <c r="E117" t="n">
-        <v>185.3339522994643</v>
+        <v>175.8854835656673</v>
       </c>
       <c r="F117" t="n">
-        <v>144719700</v>
+        <v>222775500</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>46001</v>
+        <v>46009</v>
       </c>
       <c r="B118" t="n">
-        <v>183.5561218261719</v>
+        <v>173.9278564453125</v>
       </c>
       <c r="C118" t="n">
-        <v>185.2540478736652</v>
+        <v>175.9354023122364</v>
       </c>
       <c r="D118" t="n">
-        <v>181.8182359713298</v>
+        <v>171.6106906687844</v>
       </c>
       <c r="E118" t="n">
-        <v>184.7446746314776</v>
+        <v>174.3173807251694</v>
       </c>
       <c r="F118" t="n">
-        <v>162785400</v>
+        <v>176096000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>46002</v>
+        <v>46010</v>
       </c>
       <c r="B119" t="n">
-        <v>180.7095794677734</v>
+        <v>180.7695159912109</v>
       </c>
       <c r="C119" t="n">
-        <v>181.0991189911166</v>
+        <v>181.2289470656948</v>
       </c>
       <c r="D119" t="n">
-        <v>176.4048324504213</v>
+        <v>176.1251716691968</v>
       </c>
       <c r="E119" t="n">
-        <v>180.060377409269</v>
+        <v>176.4547714783875</v>
       </c>
       <c r="F119" t="n">
-        <v>182136600</v>
+        <v>324925900</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46003</v>
+        <v>46013</v>
       </c>
       <c r="B120" t="n">
-        <v>174.8067932128906</v>
+        <v>183.4662322998047</v>
       </c>
       <c r="C120" t="n">
-        <v>182.5972942255974</v>
+        <v>183.935660967629</v>
       </c>
       <c r="D120" t="n">
-        <v>174.4072713526335</v>
+        <v>182.1278683380167</v>
       </c>
       <c r="E120" t="n">
-        <v>180.8893706584245</v>
+        <v>183.6959478478248</v>
       </c>
       <c r="F120" t="n">
-        <v>204274900</v>
+        <v>129064400</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46006</v>
+        <v>46014</v>
       </c>
       <c r="B121" t="n">
-        <v>176.0752258300781</v>
+        <v>188.9795074462891</v>
       </c>
       <c r="C121" t="n">
-        <v>178.2026358082024</v>
+        <v>189.099356383118</v>
       </c>
       <c r="D121" t="n">
-        <v>174.8167663270721</v>
+        <v>182.6771816078249</v>
       </c>
       <c r="E121" t="n">
-        <v>177.7232248413715</v>
+        <v>182.7471036477755</v>
       </c>
       <c r="F121" t="n">
-        <v>164775600</v>
+        <v>174873600</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46007</v>
+        <v>46015</v>
       </c>
       <c r="B122" t="n">
-        <v>177.5034942626953</v>
+        <v>188.3802337646484</v>
       </c>
       <c r="C122" t="n">
-        <v>178.2725604793295</v>
+        <v>188.67987134928</v>
       </c>
       <c r="D122" t="n">
-        <v>174.686922405521</v>
+        <v>186.3626902843432</v>
       </c>
       <c r="E122" t="n">
-        <v>176.0452661984462</v>
+        <v>187.711051795085</v>
       </c>
       <c r="F122" t="n">
-        <v>148588100</v>
+        <v>65528500</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46008</v>
+        <v>46017</v>
       </c>
       <c r="B123" t="n">
-        <v>170.7317504882812</v>
+        <v>190.2978973388672</v>
       </c>
       <c r="C123" t="n">
-        <v>175.9154300788059</v>
+        <v>192.4552697095027</v>
       </c>
       <c r="D123" t="n">
-        <v>170.1025131247471</v>
+        <v>187.7709805748158</v>
       </c>
       <c r="E123" t="n">
-        <v>175.8854678462756</v>
+        <v>189.6886398242026</v>
       </c>
       <c r="F123" t="n">
-        <v>222775500</v>
+        <v>139740300</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46009</v>
+        <v>46020</v>
       </c>
       <c r="B124" t="n">
-        <v>173.9278564453125</v>
+        <v>187.9907073974609</v>
       </c>
       <c r="C124" t="n">
-        <v>175.9354023122364</v>
+        <v>188.5300428516721</v>
       </c>
       <c r="D124" t="n">
-        <v>171.6106906687844</v>
+        <v>185.683523929657</v>
       </c>
       <c r="E124" t="n">
-        <v>174.3173807251694</v>
+        <v>187.4813341773615</v>
       </c>
       <c r="F124" t="n">
-        <v>176096000</v>
+        <v>120006100</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46010</v>
+        <v>46021</v>
       </c>
       <c r="B125" t="n">
-        <v>180.76953125</v>
+        <v>187.3115386962891</v>
       </c>
       <c r="C125" t="n">
-        <v>181.2289623632645</v>
+        <v>188.759784549711</v>
       </c>
       <c r="D125" t="n">
-        <v>176.1251865359559</v>
+        <v>186.7022811671161</v>
       </c>
       <c r="E125" t="n">
-        <v>176.4547863729682</v>
+        <v>188.0106981731968</v>
       </c>
       <c r="F125" t="n">
-        <v>324925900</v>
+        <v>97687300</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46013</v>
+        <v>46022</v>
       </c>
       <c r="B126" t="n">
-        <v>183.4662322998047</v>
+        <v>186.2728118896484</v>
       </c>
       <c r="C126" t="n">
-        <v>183.935660967629</v>
+        <v>190.3278636939614</v>
       </c>
       <c r="D126" t="n">
-        <v>182.1278683380167</v>
+        <v>186.262829557789</v>
       </c>
       <c r="E126" t="n">
-        <v>183.6959478478248</v>
+        <v>189.3390794328336</v>
       </c>
       <c r="F126" t="n">
-        <v>129064400</v>
+        <v>120100500</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46014</v>
+        <v>46024</v>
       </c>
       <c r="B127" t="n">
-        <v>188.9795227050781</v>
+        <v>188.6199493408203</v>
       </c>
       <c r="C127" t="n">
-        <v>189.099371651584</v>
+        <v>192.6949656802433</v>
       </c>
       <c r="D127" t="n">
-        <v>182.6771963577447</v>
+        <v>188.0306564952844</v>
       </c>
       <c r="E127" t="n">
-        <v>182.747118403341</v>
+        <v>189.6087335707417</v>
       </c>
       <c r="F127" t="n">
-        <v>174873600</v>
+        <v>148240500</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46015</v>
+        <v>46027</v>
       </c>
       <c r="B128" t="n">
-        <v>188.3802337646484</v>
+        <v>187.8908386230469</v>
       </c>
       <c r="C128" t="n">
-        <v>188.67987134928</v>
+        <v>193.3941364252797</v>
       </c>
       <c r="D128" t="n">
-        <v>186.3626902843432</v>
+        <v>185.9232371396652</v>
       </c>
       <c r="E128" t="n">
-        <v>187.711051795085</v>
+        <v>191.5264039837752</v>
       </c>
       <c r="F128" t="n">
-        <v>65528500</v>
+        <v>183529700</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46017</v>
+        <v>46028</v>
       </c>
       <c r="B129" t="n">
-        <v>190.2978973388672</v>
+        <v>187.0119171142578</v>
       </c>
       <c r="C129" t="n">
-        <v>192.4552697095027</v>
+        <v>191.935904267691</v>
       </c>
       <c r="D129" t="n">
-        <v>187.7709805748158</v>
+        <v>186.5924305704924</v>
       </c>
       <c r="E129" t="n">
-        <v>189.6886398242026</v>
+        <v>190.2879203285983</v>
       </c>
       <c r="F129" t="n">
-        <v>139740300</v>
+        <v>176862600</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46020</v>
+        <v>46029</v>
       </c>
       <c r="B130" t="n">
-        <v>187.9907073974609</v>
+        <v>188.8796234130859</v>
       </c>
       <c r="C130" t="n">
-        <v>188.5300428516721</v>
+        <v>191.1368647540468</v>
       </c>
       <c r="D130" t="n">
-        <v>185.683523929657</v>
+        <v>186.3327268208183</v>
       </c>
       <c r="E130" t="n">
-        <v>187.4813341773615</v>
+        <v>188.3402879564672</v>
       </c>
       <c r="F130" t="n">
-        <v>120006100</v>
+        <v>153543200</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46021</v>
+        <v>46030</v>
       </c>
       <c r="B131" t="n">
-        <v>187.3115386962891</v>
+        <v>184.8145904541016</v>
       </c>
       <c r="C131" t="n">
-        <v>188.759784549711</v>
+        <v>189.3191064399463</v>
       </c>
       <c r="D131" t="n">
-        <v>186.7022811671161</v>
+        <v>183.4862239788465</v>
       </c>
       <c r="E131" t="n">
-        <v>188.0106981731968</v>
+        <v>188.8796399788686</v>
       </c>
       <c r="F131" t="n">
-        <v>97687300</v>
+        <v>172457000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46022</v>
+        <v>46031</v>
       </c>
       <c r="B132" t="n">
-        <v>186.2727966308594</v>
+        <v>184.6347961425781</v>
       </c>
       <c r="C132" t="n">
-        <v>190.3278481029973</v>
+        <v>186.1129888751533</v>
       </c>
       <c r="D132" t="n">
-        <v>186.2628142998177</v>
+        <v>183.4462434137413</v>
       </c>
       <c r="E132" t="n">
-        <v>189.3390639228672</v>
+        <v>184.8545293482555</v>
       </c>
       <c r="F132" t="n">
-        <v>120100500</v>
+        <v>131327500</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46024</v>
+        <v>46034</v>
       </c>
       <c r="B133" t="n">
-        <v>188.6199493408203</v>
+        <v>184.7147064208984</v>
       </c>
       <c r="C133" t="n">
-        <v>192.6949656802433</v>
+        <v>186.8920434047358</v>
       </c>
       <c r="D133" t="n">
-        <v>188.0306564952844</v>
+        <v>182.7970472156232</v>
       </c>
       <c r="E133" t="n">
-        <v>189.6087335707417</v>
+        <v>182.9968005253017</v>
       </c>
       <c r="F133" t="n">
-        <v>148240500</v>
+        <v>137968500</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46027</v>
+        <v>46035</v>
       </c>
       <c r="B134" t="n">
-        <v>187.8908386230469</v>
+        <v>185.5836486816406</v>
       </c>
       <c r="C134" t="n">
-        <v>193.3941364252797</v>
+        <v>187.8808499298648</v>
       </c>
       <c r="D134" t="n">
-        <v>185.9232371396652</v>
+        <v>183.1765808229301</v>
       </c>
       <c r="E134" t="n">
-        <v>191.5264039837752</v>
+        <v>184.7746378408776</v>
       </c>
       <c r="F134" t="n">
-        <v>183529700</v>
+        <v>160128900</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46028</v>
+        <v>46036</v>
       </c>
       <c r="B135" t="n">
-        <v>187.0119171142578</v>
+        <v>182.9168853759766</v>
       </c>
       <c r="C135" t="n">
-        <v>191.935904267691</v>
+        <v>184.2352845745365</v>
       </c>
       <c r="D135" t="n">
-        <v>186.5924305704924</v>
+        <v>180.5797397860201</v>
       </c>
       <c r="E135" t="n">
-        <v>190.2879203285983</v>
+        <v>184.0954557419801</v>
       </c>
       <c r="F135" t="n">
-        <v>176862600</v>
+        <v>159586100</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46029</v>
+        <v>46037</v>
       </c>
       <c r="B136" t="n">
-        <v>188.8796234130859</v>
+        <v>186.8221435546875</v>
       </c>
       <c r="C136" t="n">
-        <v>191.1368647540468</v>
+        <v>189.4689092968461</v>
       </c>
       <c r="D136" t="n">
-        <v>186.3327268208183</v>
+        <v>186.103019420931</v>
       </c>
       <c r="E136" t="n">
-        <v>188.3402879564672</v>
+        <v>186.2728105024844</v>
       </c>
       <c r="F136" t="n">
-        <v>153543200</v>
+        <v>206188600</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>46030</v>
+        <v>46038</v>
       </c>
       <c r="B137" t="n">
-        <v>184.8145751953125</v>
+        <v>186.0031280517578</v>
       </c>
       <c r="C137" t="n">
-        <v>189.3190908092523</v>
+        <v>190.2080060835646</v>
       </c>
       <c r="D137" t="n">
-        <v>183.4862088297309</v>
+        <v>185.8533168796866</v>
       </c>
       <c r="E137" t="n">
-        <v>188.8796243844581</v>
+        <v>188.8496622427164</v>
       </c>
       <c r="F137" t="n">
-        <v>172457000</v>
+        <v>187967200</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46031</v>
+        <v>46042</v>
       </c>
       <c r="B138" t="n">
-        <v>184.6347961425781</v>
+        <v>177.8530731201172</v>
       </c>
       <c r="C138" t="n">
-        <v>186.1129888751533</v>
+        <v>182.1578200140757</v>
       </c>
       <c r="D138" t="n">
-        <v>183.4462434137413</v>
+        <v>177.3936268105082</v>
       </c>
       <c r="E138" t="n">
-        <v>184.8545293482555</v>
+        <v>181.6783938022576</v>
       </c>
       <c r="F138" t="n">
-        <v>131327500</v>
+        <v>223345300</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46034</v>
+        <v>46043</v>
       </c>
       <c r="B139" t="n">
-        <v>184.7147064208984</v>
+        <v>183.0966949462891</v>
       </c>
       <c r="C139" t="n">
-        <v>186.8920434047358</v>
+        <v>185.1541831063722</v>
       </c>
       <c r="D139" t="n">
-        <v>182.7970472156232</v>
+        <v>178.1826748627293</v>
       </c>
       <c r="E139" t="n">
-        <v>182.9968005253017</v>
+        <v>178.8318922054109</v>
       </c>
       <c r="F139" t="n">
-        <v>137968500</v>
+        <v>200381000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46035</v>
+        <v>46044</v>
       </c>
       <c r="B140" t="n">
-        <v>185.5836486816406</v>
+        <v>184.6148223876953</v>
       </c>
       <c r="C140" t="n">
-        <v>187.8808499298648</v>
+        <v>185.943203997088</v>
       </c>
       <c r="D140" t="n">
-        <v>183.1765808229301</v>
+        <v>183.705927301237</v>
       </c>
       <c r="E140" t="n">
-        <v>184.7746378408776</v>
+        <v>184.5249356842524</v>
       </c>
       <c r="F140" t="n">
-        <v>160128900</v>
+        <v>139636600</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>46036</v>
+        <v>46045</v>
       </c>
       <c r="B141" t="n">
-        <v>182.9169006347656</v>
+        <v>187.4413757324219</v>
       </c>
       <c r="C141" t="n">
-        <v>184.2352999433054</v>
+        <v>189.3690325020707</v>
       </c>
       <c r="D141" t="n">
-        <v>180.5797548498462</v>
+        <v>186.5924203594268</v>
       </c>
       <c r="E141" t="n">
-        <v>184.0954710990846</v>
+        <v>187.2715846578228</v>
       </c>
       <c r="F141" t="n">
-        <v>159586100</v>
+        <v>142748100</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>46037</v>
+        <v>46048</v>
       </c>
       <c r="B142" t="n">
-        <v>186.8221282958984</v>
+        <v>186.2428436279297</v>
       </c>
       <c r="C142" t="n">
-        <v>189.4688938218812</v>
+        <v>188.8896093041618</v>
       </c>
       <c r="D142" t="n">
-        <v>186.1030042208767</v>
+        <v>185.7634326307671</v>
       </c>
       <c r="E142" t="n">
-        <v>186.2727952885624</v>
+        <v>186.9320055089639</v>
       </c>
       <c r="F142" t="n">
-        <v>206188600</v>
+        <v>124799600</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>46038</v>
+        <v>46049</v>
       </c>
       <c r="B143" t="n">
-        <v>186.0031280517578</v>
+        <v>188.2903442382812</v>
       </c>
       <c r="C143" t="n">
-        <v>190.2080060835646</v>
+        <v>189.768536996047</v>
       </c>
       <c r="D143" t="n">
-        <v>185.8533168796866</v>
+        <v>185.4737723212542</v>
       </c>
       <c r="E143" t="n">
-        <v>188.8496622427164</v>
+        <v>187.0119047872081</v>
       </c>
       <c r="F143" t="n">
-        <v>187967200</v>
+        <v>143711600</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>46042</v>
+        <v>46050</v>
       </c>
       <c r="B144" t="n">
-        <v>177.8530883789062</v>
+        <v>191.2866973876953</v>
       </c>
       <c r="C144" t="n">
-        <v>182.1578356421877</v>
+        <v>192.1156881225865</v>
       </c>
       <c r="D144" t="n">
-        <v>177.3936420298793</v>
+        <v>189.6087360143659</v>
       </c>
       <c r="E144" t="n">
-        <v>181.6784093892375</v>
+        <v>191.0370019340606</v>
       </c>
       <c r="F144" t="n">
-        <v>223345300</v>
+        <v>148552700</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>46043</v>
+        <v>46051</v>
       </c>
       <c r="B145" t="n">
-        <v>183.0966949462891</v>
+        <v>192.2754821777344</v>
       </c>
       <c r="C145" t="n">
-        <v>185.1541831063722</v>
+        <v>193.244301759811</v>
       </c>
       <c r="D145" t="n">
-        <v>178.1826748627293</v>
+        <v>185.8333425036608</v>
       </c>
       <c r="E145" t="n">
-        <v>178.8318922054109</v>
+        <v>191.1069092802216</v>
       </c>
       <c r="F145" t="n">
-        <v>200381000</v>
+        <v>171764400</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>46044</v>
+        <v>46052</v>
       </c>
       <c r="B146" t="n">
-        <v>184.6148223876953</v>
+        <v>190.8971710205078</v>
       </c>
       <c r="C146" t="n">
-        <v>185.943203997088</v>
+        <v>194.2530784905911</v>
       </c>
       <c r="D146" t="n">
-        <v>183.705927301237</v>
+        <v>189.2391895686962</v>
       </c>
       <c r="E146" t="n">
-        <v>184.5249356842524</v>
+        <v>190.977075393629</v>
       </c>
       <c r="F146" t="n">
-        <v>139636600</v>
+        <v>179489500</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>46045</v>
+        <v>46055</v>
       </c>
       <c r="B147" t="n">
-        <v>187.4413757324219</v>
+        <v>185.3838958740234</v>
       </c>
       <c r="C147" t="n">
-        <v>189.3690325020707</v>
+        <v>190.0681850900544</v>
       </c>
       <c r="D147" t="n">
-        <v>186.5924203594268</v>
+        <v>184.6547894061738</v>
       </c>
       <c r="E147" t="n">
-        <v>187.2715846578228</v>
+        <v>186.9719553243457</v>
       </c>
       <c r="F147" t="n">
-        <v>142748100</v>
+        <v>165794100</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>46048</v>
+        <v>46056</v>
       </c>
       <c r="B148" t="n">
-        <v>186.2428436279297</v>
+        <v>180.1203002929688</v>
       </c>
       <c r="C148" t="n">
-        <v>188.8896093041618</v>
+        <v>186.043084099137</v>
       </c>
       <c r="D148" t="n">
-        <v>185.7634326307671</v>
+        <v>176.0153066189433</v>
       </c>
       <c r="E148" t="n">
-        <v>186.9320055089639</v>
+        <v>186.013121865328</v>
       </c>
       <c r="F148" t="n">
-        <v>124799600</v>
+        <v>204019600</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>46049</v>
+        <v>46057</v>
       </c>
       <c r="B149" t="n">
-        <v>188.2903442382812</v>
+        <v>173.9777984619141</v>
       </c>
       <c r="C149" t="n">
-        <v>189.768536996047</v>
+        <v>179.3612315773567</v>
       </c>
       <c r="D149" t="n">
-        <v>185.4737723212542</v>
+        <v>171.7005772519807</v>
       </c>
       <c r="E149" t="n">
-        <v>187.0119047872081</v>
+        <v>179.2413826421603</v>
       </c>
       <c r="F149" t="n">
-        <v>143711600</v>
+        <v>207014100</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46050</v>
+        <v>46058</v>
       </c>
       <c r="B150" t="n">
-        <v>191.2866821289062</v>
+        <v>171.6706085205078</v>
       </c>
       <c r="C150" t="n">
-        <v>192.1156727976695</v>
+        <v>176.604592702014</v>
       </c>
       <c r="D150" t="n">
-        <v>189.6087208894265</v>
+        <v>170.8216379544658</v>
       </c>
       <c r="E150" t="n">
-        <v>191.0369866951896</v>
+        <v>174.7168806029182</v>
       </c>
       <c r="F150" t="n">
-        <v>148552700</v>
+        <v>206312900</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46051</v>
+        <v>46059</v>
       </c>
       <c r="B151" t="n">
-        <v>192.2754821777344</v>
+        <v>185.1841278076172</v>
       </c>
       <c r="C151" t="n">
-        <v>193.244301759811</v>
+        <v>186.7721871314613</v>
       </c>
       <c r="D151" t="n">
-        <v>185.8333425036608</v>
+        <v>174.3872995354016</v>
       </c>
       <c r="E151" t="n">
-        <v>191.1069092802216</v>
+        <v>176.4747497339287</v>
       </c>
       <c r="F151" t="n">
-        <v>171764400</v>
+        <v>231346200</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46052</v>
+        <v>46062</v>
       </c>
       <c r="B152" t="n">
-        <v>190.8971710205078</v>
+        <v>189.8084869384766</v>
       </c>
       <c r="C152" t="n">
-        <v>194.2530784905911</v>
+        <v>193.4240874249024</v>
       </c>
       <c r="D152" t="n">
-        <v>189.2391895686962</v>
+        <v>183.7259094221984</v>
       </c>
       <c r="E152" t="n">
-        <v>190.977075393629</v>
+        <v>184.0355293423734</v>
       </c>
       <c r="F152" t="n">
-        <v>179489500</v>
+        <v>196387400</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46055</v>
+        <v>46063</v>
       </c>
       <c r="B153" t="n">
-        <v>185.3838806152344</v>
+        <v>188.3103179931641</v>
       </c>
       <c r="C153" t="n">
-        <v>190.0681694457055</v>
+        <v>192.2455208098368</v>
       </c>
       <c r="D153" t="n">
-        <v>184.6547742073969</v>
+        <v>187.890831456795</v>
       </c>
       <c r="E153" t="n">
-        <v>186.9719399348449</v>
+        <v>191.1468699498802</v>
       </c>
       <c r="F153" t="n">
-        <v>165794100</v>
+        <v>136764800</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46056</v>
+        <v>46064</v>
       </c>
       <c r="B154" t="n">
-        <v>180.1203002929688</v>
+        <v>189.8184814453125</v>
       </c>
       <c r="C154" t="n">
-        <v>186.043084099137</v>
+        <v>193.0245624433192</v>
       </c>
       <c r="D154" t="n">
-        <v>176.0153066189433</v>
+        <v>188.5400419786642</v>
       </c>
       <c r="E154" t="n">
-        <v>186.013121865328</v>
+        <v>192.2155516352278</v>
       </c>
       <c r="F154" t="n">
-        <v>204019600</v>
+        <v>144192700</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>46057</v>
+        <v>46065</v>
       </c>
       <c r="B155" t="n">
-        <v>173.9778137207031</v>
+        <v>186.7122802734375</v>
       </c>
       <c r="C155" t="n">
-        <v>179.3612473083018</v>
+        <v>193.3741533411549</v>
       </c>
       <c r="D155" t="n">
-        <v>171.7005923110452</v>
+        <v>186.2827961558022</v>
       </c>
       <c r="E155" t="n">
-        <v>179.241398362594</v>
+        <v>192.7948580430663</v>
       </c>
       <c r="F155" t="n">
-        <v>207014100</v>
+        <v>189932500</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>46058</v>
+        <v>46066</v>
       </c>
       <c r="B156" t="n">
-        <v>171.6706237792969</v>
+        <v>182.5873107910156</v>
       </c>
       <c r="C156" t="n">
-        <v>176.6046083993559</v>
+        <v>187.2716001888381</v>
       </c>
       <c r="D156" t="n">
-        <v>170.8216531377948</v>
+        <v>181.3687956932374</v>
       </c>
       <c r="E156" t="n">
-        <v>174.7168961324724</v>
+        <v>187.2516202842281</v>
       </c>
       <c r="F156" t="n">
-        <v>206312900</v>
+        <v>161888000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>46059</v>
+        <v>46070</v>
       </c>
       <c r="B157" t="n">
-        <v>185.1841430664062</v>
+        <v>184.7446746826172</v>
       </c>
       <c r="C157" t="n">
-        <v>186.7722025211031</v>
+        <v>186.9220117374899</v>
       </c>
       <c r="D157" t="n">
-        <v>174.3873139045544</v>
+        <v>178.9617194034806</v>
       </c>
       <c r="E157" t="n">
-        <v>176.4747642750831</v>
+        <v>181.5285959992061</v>
       </c>
       <c r="F157" t="n">
-        <v>231346200</v>
+        <v>162276900</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>46062</v>
+        <v>46071</v>
       </c>
       <c r="B158" t="n">
-        <v>189.8084869384766</v>
+        <v>187.7509918212891</v>
       </c>
       <c r="C158" t="n">
-        <v>193.4240874249024</v>
+        <v>190.1380796288085</v>
       </c>
       <c r="D158" t="n">
-        <v>183.7259094221984</v>
+        <v>186.5324768493971</v>
       </c>
       <c r="E158" t="n">
-        <v>184.0355293423734</v>
+        <v>188.5200580472013</v>
       </c>
       <c r="F158" t="n">
-        <v>196387400</v>
+        <v>164749100</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>46063</v>
+        <v>46072</v>
       </c>
       <c r="B159" t="n">
-        <v>188.3103179931641</v>
+        <v>187.6710968017578</v>
       </c>
       <c r="C159" t="n">
-        <v>192.2455208098368</v>
+        <v>188.200449944095</v>
       </c>
       <c r="D159" t="n">
-        <v>187.890831456795</v>
+        <v>185.4338352915633</v>
       </c>
       <c r="E159" t="n">
-        <v>191.1468699498802</v>
+        <v>186.8321237354349</v>
       </c>
       <c r="F159" t="n">
-        <v>136764800</v>
+        <v>126554500</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>46064</v>
+        <v>46073</v>
       </c>
       <c r="B160" t="n">
-        <v>189.8184967041016</v>
+        <v>189.5887756347656</v>
       </c>
       <c r="C160" t="n">
-        <v>193.024577959833</v>
+        <v>190.0981488852172</v>
       </c>
       <c r="D160" t="n">
-        <v>188.5400571346844</v>
+        <v>185.7134972299297</v>
       </c>
       <c r="E160" t="n">
-        <v>192.2155670867083</v>
+        <v>186.342734664171</v>
       </c>
       <c r="F160" t="n">
-        <v>144192700</v>
+        <v>178422300</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>46065</v>
+        <v>46076</v>
       </c>
       <c r="B161" t="n">
-        <v>186.7122802734375</v>
+        <v>191.3166656494141</v>
       </c>
       <c r="C161" t="n">
-        <v>193.3741533411549</v>
+        <v>193.7137359837344</v>
       </c>
       <c r="D161" t="n">
-        <v>186.2827961558022</v>
+        <v>189.3490641935772</v>
       </c>
       <c r="E161" t="n">
-        <v>192.7948580430663</v>
+        <v>191.1668392283931</v>
       </c>
       <c r="F161" t="n">
-        <v>189932500</v>
+        <v>171584800</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>46066</v>
+        <v>46077</v>
       </c>
       <c r="B162" t="n">
-        <v>182.5872955322266</v>
+        <v>192.6150817871094</v>
       </c>
       <c r="C162" t="n">
-        <v>187.2715845385837</v>
+        <v>193.5339592408144</v>
       </c>
       <c r="D162" t="n">
-        <v>181.3687805362794</v>
+        <v>187.171708627792</v>
       </c>
       <c r="E162" t="n">
-        <v>187.2516046356435</v>
+        <v>191.2567378902843</v>
       </c>
       <c r="F162" t="n">
-        <v>161888000</v>
+        <v>175123600</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>46070</v>
+        <v>46078</v>
       </c>
       <c r="B163" t="n">
-        <v>184.7446746826172</v>
+        <v>195.3217620849609</v>
       </c>
       <c r="C163" t="n">
-        <v>186.9220117374899</v>
+        <v>197.3892476809047</v>
       </c>
       <c r="D163" t="n">
-        <v>178.9617194034806</v>
+        <v>193.5539140704845</v>
       </c>
       <c r="E163" t="n">
-        <v>181.5285959992061</v>
+        <v>194.2131137016724</v>
       </c>
       <c r="F163" t="n">
-        <v>162276900</v>
+        <v>250637100</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>46071</v>
+        <v>46079</v>
       </c>
       <c r="B164" t="n">
-        <v>187.7509918212891</v>
+        <v>184.6647644042969</v>
       </c>
       <c r="C164" t="n">
-        <v>190.1380796288085</v>
+        <v>194.0533071271398</v>
       </c>
       <c r="D164" t="n">
-        <v>186.5324768493971</v>
+        <v>184.0954667093303</v>
       </c>
       <c r="E164" t="n">
-        <v>188.5200580472013</v>
+        <v>194.0333424642993</v>
       </c>
       <c r="F164" t="n">
-        <v>164749100</v>
+        <v>360807900</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>46072</v>
+        <v>46080</v>
       </c>
       <c r="B165" t="n">
-        <v>187.6710968017578</v>
+        <v>176.9741516113281</v>
       </c>
       <c r="C165" t="n">
-        <v>188.200449944095</v>
+        <v>182.3675672971408</v>
       </c>
       <c r="D165" t="n">
-        <v>185.4338352915633</v>
+        <v>176.1651407824763</v>
       </c>
       <c r="E165" t="n">
-        <v>186.8321237354349</v>
+        <v>181.0292033274304</v>
       </c>
       <c r="F165" t="n">
-        <v>126554500</v>
+        <v>311636500</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>46073</v>
+        <v>46083</v>
       </c>
       <c r="B166" t="n">
-        <v>189.5887756347656</v>
+        <v>182.2577056884766</v>
       </c>
       <c r="C166" t="n">
-        <v>190.0981488852172</v>
+        <v>183.2365228635074</v>
       </c>
       <c r="D166" t="n">
-        <v>185.7134972299297</v>
+        <v>174.4272597294384</v>
       </c>
       <c r="E166" t="n">
-        <v>186.342734664171</v>
+        <v>174.7968041329533</v>
       </c>
       <c r="F166" t="n">
-        <v>178422300</v>
+        <v>209095300</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>46076</v>
+        <v>46084</v>
       </c>
       <c r="B167" t="n">
-        <v>191.316650390625</v>
+        <v>179.8306579589844</v>
       </c>
       <c r="C167" t="n">
-        <v>193.7137205337629</v>
+        <v>180.6796133062517</v>
       </c>
       <c r="D167" t="n">
-        <v>189.3490490917175</v>
+        <v>176.7044661903055</v>
       </c>
       <c r="E167" t="n">
-        <v>191.1668239815537</v>
+        <v>178.2725608602819</v>
       </c>
       <c r="F167" t="n">
-        <v>171584800</v>
+        <v>178099400</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>46077</v>
+        <v>46085</v>
       </c>
       <c r="B168" t="n">
-        <v>192.6150817871094</v>
+        <v>182.8170166015625</v>
       </c>
       <c r="C168" t="n">
-        <v>193.5339592408144</v>
+        <v>184.47499807111</v>
       </c>
       <c r="D168" t="n">
-        <v>187.171708627792</v>
+        <v>179.8406510619153</v>
       </c>
       <c r="E168" t="n">
-        <v>191.2567378902843</v>
+        <v>180.2201930282506</v>
       </c>
       <c r="F168" t="n">
-        <v>175123600</v>
+        <v>177731200</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>46078</v>
+        <v>46086</v>
       </c>
       <c r="B169" t="n">
-        <v>195.3217620849609</v>
+        <v>183.1166534423828</v>
       </c>
       <c r="C169" t="n">
-        <v>197.3892476809047</v>
+        <v>183.8357775650134</v>
       </c>
       <c r="D169" t="n">
-        <v>193.5539140704845</v>
+        <v>177.6633132926684</v>
       </c>
       <c r="E169" t="n">
-        <v>194.2131137016724</v>
+        <v>180.9492987428603</v>
       </c>
       <c r="F169" t="n">
-        <v>250637100</v>
+        <v>198779700</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>46079</v>
+        <v>46087</v>
       </c>
       <c r="B170" t="n">
-        <v>184.6647644042969</v>
+        <v>177.6033782958984</v>
       </c>
       <c r="C170" t="n">
-        <v>194.0533071271398</v>
+        <v>182.5373473445644</v>
       </c>
       <c r="D170" t="n">
-        <v>184.0954667093303</v>
+        <v>176.6045965447985</v>
       </c>
       <c r="E170" t="n">
-        <v>194.0333424642993</v>
+        <v>179.6209064601764</v>
       </c>
       <c r="F170" t="n">
-        <v>360807900</v>
+        <v>189021900</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>46080</v>
+        <v>46090</v>
       </c>
       <c r="B171" t="n">
-        <v>176.9741516113281</v>
+        <v>182.427490234375</v>
       </c>
       <c r="C171" t="n">
-        <v>182.3675672971408</v>
+        <v>182.6871832569013</v>
       </c>
       <c r="D171" t="n">
-        <v>176.1651407824763</v>
+        <v>175.3461309082678</v>
       </c>
       <c r="E171" t="n">
-        <v>181.0292033274304</v>
+        <v>176.614588065421</v>
       </c>
       <c r="F171" t="n">
-        <v>311636500</v>
+        <v>177213600</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="B172" t="n">
-        <v>182.2577056884766</v>
+        <v>184.544921875</v>
       </c>
       <c r="C172" t="n">
-        <v>183.2365228635074</v>
+        <v>186.2128856921408</v>
       </c>
       <c r="D172" t="n">
-        <v>174.4272597294384</v>
+        <v>181.7882742872215</v>
       </c>
       <c r="E172" t="n">
-        <v>174.7968041329533</v>
+        <v>182.1777985889466</v>
       </c>
       <c r="F172" t="n">
-        <v>209095300</v>
+        <v>179118500</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>46084</v>
+        <v>46092</v>
       </c>
       <c r="B173" t="n">
-        <v>179.8306579589844</v>
+        <v>185.8134307861328</v>
       </c>
       <c r="C173" t="n">
-        <v>180.6796133062517</v>
+        <v>187.401576119786</v>
       </c>
       <c r="D173" t="n">
-        <v>176.7044661903055</v>
+        <v>184.2352683241476</v>
       </c>
       <c r="E173" t="n">
-        <v>178.2725608602819</v>
+        <v>185.6935753620157</v>
       </c>
       <c r="F173" t="n">
-        <v>178099400</v>
+        <v>145280400</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>46085</v>
+        <v>46093</v>
       </c>
       <c r="B174" t="n">
-        <v>182.8170166015625</v>
+        <v>182.9268035888672</v>
       </c>
       <c r="C174" t="n">
-        <v>184.47499807111</v>
+        <v>184.7247112322308</v>
       </c>
       <c r="D174" t="n">
-        <v>179.8406510619153</v>
+        <v>181.5384223166915</v>
       </c>
       <c r="E174" t="n">
-        <v>180.2201930282506</v>
+        <v>183.8357479031547</v>
       </c>
       <c r="F174" t="n">
-        <v>177731200</v>
+        <v>155762700</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>46086</v>
+        <v>46094</v>
       </c>
       <c r="B175" t="n">
-        <v>183.1166381835938</v>
+        <v>180.0401611328125</v>
       </c>
       <c r="C175" t="n">
-        <v>183.835762246301</v>
+        <v>185.873358812085</v>
       </c>
       <c r="D175" t="n">
-        <v>177.6632984882966</v>
+        <v>179.7305244593035</v>
       </c>
       <c r="E175" t="n">
-        <v>180.9492836646731</v>
+        <v>184.7047227018935</v>
       </c>
       <c r="F175" t="n">
-        <v>198779700</v>
+        <v>160988400</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>46087</v>
+        <v>46097</v>
       </c>
       <c r="B176" t="n">
-        <v>177.6033935546875</v>
+        <v>183.0067138671875</v>
       </c>
       <c r="C176" t="n">
-        <v>182.5373630272553</v>
+        <v>188.6601286896836</v>
       </c>
       <c r="D176" t="n">
-        <v>176.6046117177772</v>
+        <v>181.1988233361375</v>
       </c>
       <c r="E176" t="n">
-        <v>179.6209218923013</v>
+        <v>182.7570048934839</v>
       </c>
       <c r="F176" t="n">
-        <v>189021900</v>
+        <v>217307400</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>46090</v>
+        <v>46098</v>
       </c>
       <c r="B177" t="n">
-        <v>182.427490234375</v>
+        <v>181.7182006835938</v>
       </c>
       <c r="C177" t="n">
-        <v>182.6871832569013</v>
+        <v>185.1841623368753</v>
       </c>
       <c r="D177" t="n">
-        <v>175.3461309082678</v>
+        <v>181.4684917186082</v>
       </c>
       <c r="E177" t="n">
-        <v>176.614588065421</v>
+        <v>184.8445618023411</v>
       </c>
       <c r="F177" t="n">
-        <v>177213600</v>
+        <v>182497800</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>46091</v>
+        <v>46099</v>
       </c>
       <c r="B178" t="n">
-        <v>184.5449066162109</v>
+        <v>180.1899871826172</v>
       </c>
       <c r="C178" t="n">
-        <v>186.2128702954389</v>
+        <v>183.1665290872618</v>
       </c>
       <c r="D178" t="n">
-        <v>181.7882592563612</v>
+        <v>180.1200765961462</v>
       </c>
       <c r="E178" t="n">
-        <v>182.1777835258792</v>
+        <v>182.2675676480169</v>
       </c>
       <c r="F178" t="n">
-        <v>179118500</v>
+        <v>156683100</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>46092</v>
+        <v>46100</v>
       </c>
       <c r="B179" t="n">
-        <v>185.8134307861328</v>
+        <v>178.3521270751953</v>
       </c>
       <c r="C179" t="n">
-        <v>187.401576119786</v>
+        <v>179.7704721543678</v>
       </c>
       <c r="D179" t="n">
-        <v>184.2352683241476</v>
+        <v>175.5853475010711</v>
       </c>
       <c r="E179" t="n">
-        <v>185.6935753620157</v>
+        <v>177.8027643090659</v>
       </c>
       <c r="F179" t="n">
-        <v>145280400</v>
+        <v>170968500</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>46093</v>
+        <v>46101</v>
       </c>
       <c r="B180" t="n">
-        <v>182.9268035888672</v>
+        <v>172.4989471435547</v>
       </c>
       <c r="C180" t="n">
-        <v>184.7247112322308</v>
+        <v>178.0524719954723</v>
       </c>
       <c r="D180" t="n">
-        <v>181.5384223166915</v>
+        <v>171.5200922843023</v>
       </c>
       <c r="E180" t="n">
-        <v>183.8357479031547</v>
+        <v>177.7927801629024</v>
       </c>
       <c r="F180" t="n">
-        <v>155762700</v>
+        <v>241323500</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>46094</v>
+        <v>46104</v>
       </c>
       <c r="B181" t="n">
-        <v>180.0401611328125</v>
+        <v>175.4355316162109</v>
       </c>
       <c r="C181" t="n">
-        <v>185.873358812085</v>
+        <v>178.1623492741198</v>
       </c>
       <c r="D181" t="n">
-        <v>179.7305244593035</v>
+        <v>174.5565511733872</v>
       </c>
       <c r="E181" t="n">
-        <v>184.7047227018935</v>
+        <v>177.0536408486584</v>
       </c>
       <c r="F181" t="n">
-        <v>160988400</v>
+        <v>182836300</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>46097</v>
+        <v>46105</v>
       </c>
       <c r="B182" t="n">
-        <v>183.0067138671875</v>
+        <v>174.9960327148438</v>
       </c>
       <c r="C182" t="n">
-        <v>188.6601286896836</v>
+        <v>176.0148495193074</v>
       </c>
       <c r="D182" t="n">
-        <v>181.1988233361375</v>
+        <v>173.777451794472</v>
       </c>
       <c r="E182" t="n">
-        <v>182.7570048934839</v>
+        <v>174.6264683383626</v>
       </c>
       <c r="F182" t="n">
-        <v>217307400</v>
+        <v>147667800</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>46098</v>
+        <v>46106</v>
       </c>
       <c r="B183" t="n">
-        <v>181.7182006835938</v>
+        <v>178.4719848632812</v>
       </c>
       <c r="C183" t="n">
-        <v>185.1841623368753</v>
+        <v>181.0090364928079</v>
       </c>
       <c r="D183" t="n">
-        <v>181.4684917186082</v>
+        <v>176.6441286442695</v>
       </c>
       <c r="E183" t="n">
-        <v>184.8445618023411</v>
+        <v>176.8938376102687</v>
       </c>
       <c r="F183" t="n">
-        <v>182497800</v>
+        <v>162602100</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>46099</v>
+        <v>46107</v>
       </c>
       <c r="B184" t="n">
-        <v>180.1899871826172</v>
+        <v>171.0406646728516</v>
       </c>
       <c r="C184" t="n">
-        <v>183.1665290872618</v>
+        <v>176.3045188821592</v>
       </c>
       <c r="D184" t="n">
-        <v>180.1200765961462</v>
+        <v>170.9407749866337</v>
       </c>
       <c r="E184" t="n">
-        <v>182.2675676480169</v>
+        <v>175.865043889469</v>
       </c>
       <c r="F184" t="n">
-        <v>156683100</v>
+        <v>186152200</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>46100</v>
+        <v>46108</v>
       </c>
       <c r="B185" t="n">
-        <v>178.3521270751953</v>
+        <v>167.3249816894531</v>
       </c>
       <c r="C185" t="n">
-        <v>179.7704721543678</v>
+        <v>170.7709622378681</v>
       </c>
       <c r="D185" t="n">
-        <v>175.5853475010711</v>
+        <v>166.8155656643923</v>
       </c>
       <c r="E185" t="n">
-        <v>177.8027643090659</v>
+        <v>169.802090268232</v>
       </c>
       <c r="F185" t="n">
-        <v>170968500</v>
+        <v>196212700</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>46101</v>
+        <v>46111</v>
       </c>
       <c r="B186" t="n">
-        <v>172.4989471435547</v>
+        <v>164.9777221679688</v>
       </c>
       <c r="C186" t="n">
-        <v>178.0524719954723</v>
+        <v>169.2527385590681</v>
       </c>
       <c r="D186" t="n">
-        <v>171.5200922843023</v>
+        <v>164.0787759631308</v>
       </c>
       <c r="E186" t="n">
-        <v>177.7927801629024</v>
+        <v>168.5835203415062</v>
       </c>
       <c r="F186" t="n">
-        <v>241323500</v>
+        <v>185627000</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>46104</v>
+        <v>46112</v>
       </c>
       <c r="B187" t="n">
-        <v>175.4355316162109</v>
+        <v>174.1969757080078</v>
       </c>
       <c r="C187" t="n">
-        <v>178.1623492741198</v>
+        <v>174.4167208263551</v>
       </c>
       <c r="D187" t="n">
-        <v>174.5565511733872</v>
+        <v>166.7656493784466</v>
       </c>
       <c r="E187" t="n">
-        <v>177.0536408486584</v>
+        <v>166.7756322507255</v>
       </c>
       <c r="F187" t="n">
-        <v>182836300</v>
+        <v>226181300</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>46105</v>
+        <v>46113</v>
       </c>
       <c r="B188" t="n">
-        <v>174.9960327148438</v>
+        <v>175.54541015625</v>
       </c>
       <c r="C188" t="n">
-        <v>176.0148495193074</v>
+        <v>177.163519443862</v>
       </c>
       <c r="D188" t="n">
-        <v>173.777451794472</v>
+        <v>174.5465742520892</v>
       </c>
       <c r="E188" t="n">
-        <v>174.6264683383626</v>
+        <v>175.7951191322902</v>
       </c>
       <c r="F188" t="n">
-        <v>147667800</v>
+        <v>168132000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="B189" t="n">
-        <v>178.4719848632812</v>
+        <v>177.1834869384766</v>
       </c>
       <c r="C189" t="n">
-        <v>181.0090364928079</v>
+        <v>177.2833766176975</v>
       </c>
       <c r="D189" t="n">
-        <v>176.6441286442695</v>
+        <v>171.170490985778</v>
       </c>
       <c r="E189" t="n">
-        <v>176.8938376102687</v>
+        <v>171.9795455679816</v>
       </c>
       <c r="F189" t="n">
-        <v>162602100</v>
+        <v>143143200</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>46107</v>
+        <v>46118</v>
       </c>
       <c r="B190" t="n">
-        <v>171.0406646728516</v>
+        <v>177.4331970214844</v>
       </c>
       <c r="C190" t="n">
-        <v>176.3045188821592</v>
+        <v>177.5830163002413</v>
       </c>
       <c r="D190" t="n">
-        <v>170.9407749866337</v>
+        <v>175.5553807755963</v>
       </c>
       <c r="E190" t="n">
-        <v>175.865043889469</v>
+        <v>176.953760088437</v>
       </c>
       <c r="F190" t="n">
-        <v>186152200</v>
+        <v>107564300</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>46108</v>
+        <v>46119</v>
       </c>
       <c r="B191" t="n">
-        <v>167.3249816894531</v>
+        <v>177.8926696777344</v>
       </c>
       <c r="C191" t="n">
-        <v>170.7709622378681</v>
+        <v>178.0225079733855</v>
       </c>
       <c r="D191" t="n">
-        <v>166.8155656643923</v>
+        <v>173.4578360976707</v>
       </c>
       <c r="E191" t="n">
-        <v>169.802090268232</v>
+        <v>175.5254183666853</v>
       </c>
       <c r="F191" t="n">
-        <v>196212700</v>
+        <v>132534900</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>46111</v>
+        <v>46120</v>
       </c>
       <c r="B192" t="n">
-        <v>164.9777221679688</v>
+        <v>181.8680419921875</v>
       </c>
       <c r="C192" t="n">
-        <v>169.2527385590681</v>
+        <v>185.0443328296099</v>
       </c>
       <c r="D192" t="n">
-        <v>164.0787759631308</v>
+        <v>180.090115314443</v>
       </c>
       <c r="E192" t="n">
-        <v>168.5835203415062</v>
+        <v>184.2852230345028</v>
       </c>
       <c r="F192" t="n">
-        <v>185627000</v>
+        <v>147732700</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>46112</v>
+        <v>46121</v>
       </c>
       <c r="B193" t="n">
-        <v>174.1969757080078</v>
+        <v>183.6959075927734</v>
       </c>
       <c r="C193" t="n">
-        <v>174.4167208263551</v>
+        <v>183.8657078609029</v>
       </c>
       <c r="D193" t="n">
-        <v>166.7656493784466</v>
+        <v>180.4097290618993</v>
       </c>
       <c r="E193" t="n">
-        <v>166.7756322507255</v>
+        <v>181.6283100364998</v>
       </c>
       <c r="F193" t="n">
-        <v>226181300</v>
+        <v>116428500</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="B194" t="n">
-        <v>175.54541015625</v>
+        <v>188.4104156494141</v>
       </c>
       <c r="C194" t="n">
-        <v>177.163519443862</v>
+        <v>189.7788159186465</v>
       </c>
       <c r="D194" t="n">
-        <v>174.5465742520892</v>
+        <v>184.0854544892923</v>
       </c>
       <c r="E194" t="n">
-        <v>175.7951191322902</v>
+        <v>184.0954373612556</v>
       </c>
       <c r="F194" t="n">
-        <v>168132000</v>
+        <v>160459500</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>46114</v>
+        <v>46125</v>
       </c>
       <c r="B195" t="n">
-        <v>177.1834869384766</v>
+        <v>189.0896148681641</v>
       </c>
       <c r="C195" t="n">
-        <v>177.2833766176975</v>
+        <v>189.4392135167763</v>
       </c>
       <c r="D195" t="n">
-        <v>171.170490985778</v>
+        <v>185.5237787610374</v>
       </c>
       <c r="E195" t="n">
-        <v>171.9795455679816</v>
+        <v>185.813434455382</v>
       </c>
       <c r="F195" t="n">
-        <v>143143200</v>
+        <v>133648200</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>46118</v>
+        <v>46126</v>
       </c>
       <c r="B196" t="n">
-        <v>177.4331970214844</v>
+        <v>196.2812347412109</v>
       </c>
       <c r="C196" t="n">
-        <v>177.5830163002413</v>
+        <v>196.2812347412109</v>
       </c>
       <c r="D196" t="n">
-        <v>175.5553807755963</v>
+        <v>190.5479265019375</v>
       </c>
       <c r="E196" t="n">
-        <v>176.953760088437</v>
+        <v>190.6178370887202</v>
       </c>
       <c r="F196" t="n">
-        <v>107564300</v>
+        <v>161307000</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="B197" t="n">
-        <v>177.8926696777344</v>
+        <v>198.6384887695312</v>
       </c>
       <c r="C197" t="n">
-        <v>178.0225079733855</v>
+        <v>200.166706463506</v>
       </c>
       <c r="D197" t="n">
-        <v>173.4578360976707</v>
+        <v>195.5121427945441</v>
       </c>
       <c r="E197" t="n">
-        <v>175.5254183666853</v>
+        <v>196.3111993145372</v>
       </c>
       <c r="F197" t="n">
-        <v>132534900</v>
+        <v>185338400</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>46120</v>
+        <v>46128</v>
       </c>
       <c r="B198" t="n">
-        <v>181.8680419921875</v>
+        <v>198.1190948486328</v>
       </c>
       <c r="C198" t="n">
-        <v>185.0443328296099</v>
+        <v>199.6173486077875</v>
       </c>
       <c r="D198" t="n">
-        <v>180.090115314443</v>
+        <v>195.58204328149</v>
       </c>
       <c r="E198" t="n">
-        <v>184.2852230345028</v>
+        <v>197.2001524642489</v>
       </c>
       <c r="F198" t="n">
-        <v>147732700</v>
+        <v>134012900</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>46121</v>
+        <v>46129</v>
       </c>
       <c r="B199" t="n">
-        <v>183.6959075927734</v>
+        <v>201.4452056884766</v>
       </c>
       <c r="C199" t="n">
-        <v>183.8657078609029</v>
+        <v>201.4651866728423</v>
       </c>
       <c r="D199" t="n">
-        <v>180.4097290618993</v>
+        <v>199.0380228877802</v>
       </c>
       <c r="E199" t="n">
-        <v>181.6283100364998</v>
+        <v>199.66727910556</v>
       </c>
       <c r="F199" t="n">
-        <v>116428500</v>
+        <v>160324400</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>46122</v>
+        <v>46132</v>
       </c>
       <c r="B200" t="n">
-        <v>188.4104156494141</v>
+        <v>201.8247680664062</v>
       </c>
       <c r="C200" t="n">
-        <v>189.7788159186465</v>
+        <v>201.9346406188145</v>
       </c>
       <c r="D200" t="n">
-        <v>184.0854544892923</v>
+        <v>197.6096795882359</v>
       </c>
       <c r="E200" t="n">
-        <v>184.0954373612556</v>
+        <v>199.7471876833392</v>
       </c>
       <c r="F200" t="n">
-        <v>160459500</v>
+        <v>119381400</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="B201" t="n">
-        <v>189.0896148681641</v>
+        <v>199.6473236083984</v>
       </c>
       <c r="C201" t="n">
-        <v>189.4392135167763</v>
+        <v>202.5139777504753</v>
       </c>
       <c r="D201" t="n">
-        <v>185.5237787610374</v>
+        <v>198.7683431434998</v>
       </c>
       <c r="E201" t="n">
-        <v>185.813434455382</v>
+        <v>201.8947043725837</v>
       </c>
       <c r="F201" t="n">
-        <v>133648200</v>
+        <v>107945300</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>46126</v>
+        <v>46134</v>
       </c>
       <c r="B202" t="n">
-        <v>196.2812347412109</v>
+        <v>202.2642669677734</v>
       </c>
       <c r="C202" t="n">
-        <v>196.2812347412109</v>
+        <v>202.2642669677734</v>
       </c>
       <c r="D202" t="n">
-        <v>190.5479265019375</v>
+        <v>198.7683413658613</v>
       </c>
       <c r="E202" t="n">
-        <v>190.6178370887202</v>
+        <v>200.7560302662893</v>
       </c>
       <c r="F202" t="n">
-        <v>161307000</v>
+        <v>107501000</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>46127</v>
+        <v>46135</v>
       </c>
       <c r="B203" t="n">
-        <v>198.6384887695312</v>
+        <v>199.4075927734375</v>
       </c>
       <c r="C203" t="n">
-        <v>200.166706463506</v>
+        <v>203.5927175135199</v>
       </c>
       <c r="D203" t="n">
-        <v>195.5121427945441</v>
+        <v>196.9904117933692</v>
       </c>
       <c r="E203" t="n">
-        <v>196.3111993145372</v>
+        <v>202.224317246715</v>
       </c>
       <c r="F203" t="n">
-        <v>185338400</v>
+        <v>113561800</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>46128</v>
+        <v>46136</v>
       </c>
       <c r="B204" t="n">
-        <v>198.1190948486328</v>
+        <v>208.0275421142578</v>
       </c>
       <c r="C204" t="n">
-        <v>199.6173486077875</v>
+        <v>210.7044148169522</v>
       </c>
       <c r="D204" t="n">
-        <v>195.58204328149</v>
+        <v>199.5773843053898</v>
       </c>
       <c r="E204" t="n">
-        <v>197.2001524642489</v>
+        <v>199.7272188241683</v>
       </c>
       <c r="F204" t="n">
-        <v>134012900</v>
+        <v>214134400</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>46129</v>
+        <v>46139</v>
       </c>
       <c r="B205" t="n">
-        <v>201.4452056884766</v>
+        <v>216.3578338623047</v>
       </c>
       <c r="C205" t="n">
-        <v>201.4651866728423</v>
+        <v>216.5775789683675</v>
       </c>
       <c r="D205" t="n">
-        <v>199.0380228877802</v>
+        <v>207.1385832434889</v>
       </c>
       <c r="E205" t="n">
-        <v>199.66727910556</v>
+        <v>209.4059296471886</v>
       </c>
       <c r="F205" t="n">
-        <v>160324400</v>
+        <v>187172400</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>46132</v>
+        <v>46140</v>
       </c>
       <c r="B206" t="n">
-        <v>201.8247680664062</v>
+        <v>212.9218444824219</v>
       </c>
       <c r="C206" t="n">
-        <v>201.9346406188145</v>
+        <v>214.4800260296235</v>
       </c>
       <c r="D206" t="n">
-        <v>197.6096795882359</v>
+        <v>207.957628898232</v>
       </c>
       <c r="E206" t="n">
-        <v>199.7471876833392</v>
+        <v>209.2461357291284</v>
       </c>
       <c r="F206" t="n">
-        <v>119381400</v>
+        <v>180275400</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>46133</v>
+        <v>46141</v>
       </c>
       <c r="B207" t="n">
-        <v>199.6473236083984</v>
+        <v>209.0064086914062</v>
       </c>
       <c r="C207" t="n">
-        <v>202.5139777504753</v>
+        <v>212.4723704275781</v>
       </c>
       <c r="D207" t="n">
-        <v>198.7683431434998</v>
+        <v>207.3383545943335</v>
       </c>
       <c r="E207" t="n">
-        <v>201.8947043725837</v>
+        <v>212.4523894424142</v>
       </c>
       <c r="F207" t="n">
-        <v>107945300</v>
+        <v>123711800</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>46134</v>
+        <v>46142</v>
       </c>
       <c r="B208" t="n">
-        <v>202.2642669677734</v>
+        <v>199.3376770019531</v>
       </c>
       <c r="C208" t="n">
-        <v>202.2642669677734</v>
+        <v>210.0551813566716</v>
       </c>
       <c r="D208" t="n">
-        <v>198.7683413658613</v>
+        <v>198.4686794524716</v>
       </c>
       <c r="E208" t="n">
-        <v>200.7560302662893</v>
+        <v>209.6856017299396</v>
       </c>
       <c r="F208" t="n">
-        <v>107501000</v>
+        <v>225239200</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>46135</v>
+        <v>46143</v>
       </c>
       <c r="B209" t="n">
-        <v>199.4075927734375</v>
+        <v>198.2189788818359</v>
       </c>
       <c r="C209" t="n">
-        <v>203.5927175135199</v>
+        <v>202.7636852194425</v>
       </c>
       <c r="D209" t="n">
-        <v>196.9904117933692</v>
+        <v>196.8905253221647</v>
       </c>
       <c r="E209" t="n">
-        <v>202.224317246715</v>
+        <v>201.0456862731779</v>
       </c>
       <c r="F209" t="n">
-        <v>113561800</v>
+        <v>128647000</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>46136</v>
+        <v>46146</v>
       </c>
       <c r="B210" t="n">
-        <v>208.0275421142578</v>
+        <v>198.2489318847656</v>
       </c>
       <c r="C210" t="n">
-        <v>210.7044148169522</v>
+        <v>201.4951483423171</v>
       </c>
       <c r="D210" t="n">
-        <v>199.5773843053898</v>
+        <v>194.5132956232549</v>
       </c>
       <c r="E210" t="n">
-        <v>199.7272188241683</v>
+        <v>199.2677487020073</v>
       </c>
       <c r="F210" t="n">
-        <v>214134400</v>
+        <v>125368100</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>46139</v>
+        <v>46147</v>
       </c>
       <c r="B211" t="n">
-        <v>216.3578338623047</v>
+        <v>196.271240234375</v>
       </c>
       <c r="C211" t="n">
-        <v>216.5775789683675</v>
+        <v>200.0068917184803</v>
       </c>
       <c r="D211" t="n">
-        <v>207.1385832434889</v>
+        <v>195.8017861758555</v>
       </c>
       <c r="E211" t="n">
-        <v>209.4059296471886</v>
+        <v>199.0679836014414</v>
       </c>
       <c r="F211" t="n">
-        <v>187172400</v>
+        <v>113406600</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="B212" t="n">
-        <v>212.9218444824219</v>
+        <v>207.5880584716797</v>
       </c>
       <c r="C212" t="n">
-        <v>214.4800260296235</v>
+        <v>208.0275486883452</v>
       </c>
       <c r="D212" t="n">
-        <v>207.957628898232</v>
+        <v>198.3787906294548</v>
       </c>
       <c r="E212" t="n">
-        <v>209.2461357291284</v>
+        <v>199.657299310104</v>
       </c>
       <c r="F212" t="n">
-        <v>180275400</v>
+        <v>188362800</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>46141</v>
+        <v>46149</v>
       </c>
       <c r="B213" t="n">
-        <v>209.0064086914062</v>
+        <v>211.2537841796875</v>
       </c>
       <c r="C213" t="n">
-        <v>212.4723704275781</v>
+        <v>213.9506379507975</v>
       </c>
       <c r="D213" t="n">
-        <v>207.3383545943335</v>
+        <v>206.2596048846594</v>
       </c>
       <c r="E213" t="n">
-        <v>212.4523894424142</v>
+        <v>208.0974592073836</v>
       </c>
       <c r="F213" t="n">
-        <v>123711800</v>
+        <v>168307900</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>46142</v>
+        <v>46150</v>
       </c>
       <c r="B214" t="n">
-        <v>199.3376770019531</v>
+        <v>214.9494781494141</v>
       </c>
       <c r="C214" t="n">
-        <v>210.0551813566716</v>
+        <v>217.5464575316693</v>
       </c>
       <c r="D214" t="n">
-        <v>198.4686794524716</v>
+        <v>212.642169707093</v>
       </c>
       <c r="E214" t="n">
-        <v>209.6856017299396</v>
+        <v>212.7820061205359</v>
       </c>
       <c r="F214" t="n">
-        <v>225239200</v>
+        <v>136421400</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>46143</v>
+        <v>46153</v>
       </c>
       <c r="B215" t="n">
-        <v>198.2189788818359</v>
+        <v>219.1845397949219</v>
       </c>
       <c r="C215" t="n">
-        <v>202.7636852194425</v>
+        <v>222.0412109151315</v>
       </c>
       <c r="D215" t="n">
-        <v>196.8905253221647</v>
+        <v>213.640997818865</v>
       </c>
       <c r="E215" t="n">
-        <v>201.0456862731779</v>
+        <v>213.7908170988833</v>
       </c>
       <c r="F215" t="n">
-        <v>128647000</v>
+        <v>160685800</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="B216" t="n">
-        <v>198.2489318847656</v>
+        <v>220.5229797363281</v>
       </c>
       <c r="C216" t="n">
-        <v>201.4951483423171</v>
+        <v>223.4895234569154</v>
       </c>
       <c r="D216" t="n">
-        <v>194.5132956232549</v>
+        <v>214.6698009927987</v>
       </c>
       <c r="E216" t="n">
-        <v>199.2677487020073</v>
+        <v>218.2955800381889</v>
       </c>
       <c r="F216" t="n">
-        <v>125368100</v>
+        <v>159176600</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="B217" t="n">
-        <v>196.271240234375</v>
+        <v>225.5671081542969</v>
       </c>
       <c r="C217" t="n">
-        <v>200.0068917184803</v>
+        <v>227.5747627822776</v>
       </c>
       <c r="D217" t="n">
-        <v>195.8017861758555</v>
+        <v>221.3120728008497</v>
       </c>
       <c r="E217" t="n">
-        <v>199.0679836014414</v>
+        <v>224.6681467194947</v>
       </c>
       <c r="F217" t="n">
-        <v>113406600</v>
+        <v>150405400</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>46148</v>
+        <v>46156</v>
       </c>
       <c r="B218" t="n">
-        <v>207.5880584716797</v>
+        <v>235.465576171875</v>
       </c>
       <c r="C218" t="n">
-        <v>208.0275486883452</v>
+        <v>236.2646326841873</v>
       </c>
       <c r="D218" t="n">
-        <v>198.3787906294548</v>
+        <v>229.0330706569891</v>
       </c>
       <c r="E218" t="n">
-        <v>199.657299310104</v>
+        <v>229.5824334399734</v>
       </c>
       <c r="F218" t="n">
-        <v>188362800</v>
+        <v>180782900</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>46149</v>
+        <v>46157</v>
       </c>
       <c r="B219" t="n">
-        <v>211.2537841796875</v>
+        <v>225.0577087402344</v>
       </c>
       <c r="C219" t="n">
-        <v>213.9506379507975</v>
+        <v>231.2305071888046</v>
       </c>
       <c r="D219" t="n">
-        <v>206.2596048846594</v>
+        <v>223.9789641563916</v>
       </c>
       <c r="E219" t="n">
-        <v>208.0974592073836</v>
+        <v>229.4925272635535</v>
       </c>
       <c r="F219" t="n">
-        <v>168307900</v>
+        <v>180977600</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>46150</v>
+        <v>46160</v>
       </c>
       <c r="B220" t="n">
-        <v>214.9494781494141</v>
+        <v>222.0612030029297</v>
       </c>
       <c r="C220" t="n">
-        <v>217.5464575316693</v>
+        <v>229.7322553439391</v>
       </c>
       <c r="D220" t="n">
-        <v>212.642169707093</v>
+        <v>218.1157890335498</v>
       </c>
       <c r="E220" t="n">
-        <v>212.7820061205359</v>
+        <v>229.6024018007467</v>
       </c>
       <c r="F220" t="n">
-        <v>136421400</v>
+        <v>146280900</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>46153</v>
+        <v>46161</v>
       </c>
       <c r="B221" t="n">
-        <v>219.1845397949219</v>
+        <v>220.3531799316406</v>
       </c>
       <c r="C221" t="n">
-        <v>222.0412109151315</v>
+        <v>224.2186698370523</v>
       </c>
       <c r="D221" t="n">
-        <v>213.640997818865</v>
+        <v>217.6563261548179</v>
       </c>
       <c r="E221" t="n">
-        <v>213.7908170988833</v>
+        <v>219.3643269423611</v>
       </c>
       <c r="F221" t="n">
-        <v>160685800</v>
+        <v>140948200</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>46154</v>
+        <v>46162</v>
       </c>
       <c r="B222" t="n">
-        <v>220.5229797363281</v>
+        <v>223.2098541259766</v>
       </c>
       <c r="C222" t="n">
-        <v>223.4895234569154</v>
+        <v>225.8667612103758</v>
       </c>
       <c r="D222" t="n">
-        <v>214.6698009927987</v>
+        <v>220.2433103590018</v>
       </c>
       <c r="E222" t="n">
-        <v>218.2955800381889</v>
+        <v>222.9201831873553</v>
       </c>
       <c r="F222" t="n">
-        <v>159176600</v>
+        <v>184201600</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>46155</v>
+        <v>46163</v>
       </c>
       <c r="B223" t="n">
-        <v>225.5671081542969</v>
+        <v>219.2544555664062</v>
       </c>
       <c r="C223" t="n">
-        <v>227.5747627822776</v>
+        <v>227.1352699433697</v>
       </c>
       <c r="D223" t="n">
-        <v>221.3120728008497</v>
+        <v>217.6762930684293</v>
       </c>
       <c r="E223" t="n">
-        <v>224.6681467194947</v>
+        <v>222.0312180559658</v>
       </c>
       <c r="F223" t="n">
-        <v>150405400</v>
+        <v>203381800</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>46156</v>
+        <v>46164</v>
       </c>
       <c r="B224" t="n">
-        <v>235.465576171875</v>
+        <v>215.0793304443359</v>
       </c>
       <c r="C224" t="n">
-        <v>236.2646326841873</v>
+        <v>220.752710889455</v>
       </c>
       <c r="D224" t="n">
-        <v>229.0330706569891</v>
+        <v>214.5499486507254</v>
       </c>
       <c r="E224" t="n">
-        <v>229.5824334399734</v>
+        <v>220.6428383337419</v>
       </c>
       <c r="F224" t="n">
-        <v>180782900</v>
+        <v>169275700</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>46157</v>
+        <v>46168</v>
       </c>
       <c r="B225" t="n">
-        <v>225.0577087402344</v>
+        <v>214.6098785400391</v>
       </c>
       <c r="C225" t="n">
-        <v>231.2305071888046</v>
+        <v>217.9260057479501</v>
       </c>
       <c r="D225" t="n">
-        <v>223.9789641563916</v>
+        <v>211.7532073035669</v>
       </c>
       <c r="E225" t="n">
-        <v>229.4925272635535</v>
+        <v>216.287915508639</v>
       </c>
       <c r="F225" t="n">
-        <v>180977600</v>
+        <v>187202600</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>46160</v>
+        <v>46169</v>
       </c>
       <c r="B226" t="n">
-        <v>222.0612030029297</v>
+        <v>212.3525085449219</v>
       </c>
       <c r="C226" t="n">
-        <v>229.7322553439391</v>
+        <v>213.9006919249857</v>
       </c>
       <c r="D226" t="n">
-        <v>218.1157890335498</v>
+        <v>208.53694826896</v>
       </c>
       <c r="E226" t="n">
-        <v>229.6024018007467</v>
+        <v>213.8707280686635</v>
       </c>
       <c r="F226" t="n">
-        <v>146280900</v>
+        <v>167601200</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>46161</v>
+        <v>46170</v>
       </c>
       <c r="B227" t="n">
-        <v>220.3531799316406</v>
+        <v>214.0005798339844</v>
       </c>
       <c r="C227" t="n">
-        <v>224.2186698370523</v>
+        <v>215.2691056248748</v>
       </c>
       <c r="D227" t="n">
-        <v>217.6563261548179</v>
+        <v>210.9741084423121</v>
       </c>
       <c r="E227" t="n">
-        <v>219.3643269423611</v>
+        <v>211.03403615446</v>
       </c>
       <c r="F227" t="n">
-        <v>140948200</v>
+        <v>143996000</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>46162</v>
+        <v>46171</v>
       </c>
       <c r="B228" t="n">
-        <v>223.2098541259766</v>
+        <v>210.8942108154297</v>
       </c>
       <c r="C228" t="n">
-        <v>225.8667612103758</v>
+        <v>217.6063892667686</v>
       </c>
       <c r="D228" t="n">
-        <v>220.2433103590018</v>
+        <v>210.8842279432229</v>
       </c>
       <c r="E228" t="n">
-        <v>222.9201831873553</v>
+        <v>214.3302087418325</v>
       </c>
       <c r="F228" t="n">
-        <v>184201600</v>
+        <v>289410600</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>46163</v>
+        <v>46174</v>
       </c>
       <c r="B229" t="n">
-        <v>219.2544555664062</v>
+        <v>224.0988159179688</v>
       </c>
       <c r="C229" t="n">
-        <v>227.1352699433697</v>
+        <v>224.6082167237973</v>
       </c>
       <c r="D229" t="n">
-        <v>217.6762930684293</v>
+        <v>215.448893644638</v>
       </c>
       <c r="E229" t="n">
-        <v>222.0312180559658</v>
+        <v>215.4788575013911</v>
       </c>
       <c r="F229" t="n">
-        <v>203381800</v>
+        <v>212850700</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>46164</v>
+        <v>46175</v>
       </c>
       <c r="B230" t="n">
-        <v>215.0793304443359</v>
+        <v>222.5606079101562</v>
       </c>
       <c r="C230" t="n">
-        <v>220.752710889455</v>
+        <v>232.0095863674792</v>
       </c>
       <c r="D230" t="n">
-        <v>214.5499486507254</v>
+        <v>221.0923180144814</v>
       </c>
       <c r="E230" t="n">
-        <v>220.6428383337419</v>
+        <v>226.9155175162366</v>
       </c>
       <c r="F230" t="n">
-        <v>169275700</v>
+        <v>193362900</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>46168</v>
+        <v>46176</v>
       </c>
       <c r="B231" t="n">
-        <v>214.6098785400391</v>
+        <v>214.5</v>
       </c>
       <c r="C231" t="n">
-        <v>217.9260057479501</v>
+        <v>222.5606126707563</v>
       </c>
       <c r="D231" t="n">
-        <v>211.7532073035669</v>
+        <v>214.2602739078757</v>
       </c>
       <c r="E231" t="n">
-        <v>216.287915508639</v>
+        <v>221.4618871331354</v>
       </c>
       <c r="F231" t="n">
-        <v>187202600</v>
+        <v>160907000</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>46169</v>
+        <v>46177</v>
       </c>
       <c r="B232" t="n">
-        <v>212.3525085449219</v>
+        <v>218.6600036621094</v>
       </c>
       <c r="C232" t="n">
-        <v>213.9006919249857</v>
+        <v>221.6000061035156</v>
       </c>
       <c r="D232" t="n">
-        <v>208.53694826896</v>
+        <v>210.9700012207031</v>
       </c>
       <c r="E232" t="n">
-        <v>213.8707280686635</v>
+        <v>213.9100036621094</v>
       </c>
       <c r="F232" t="n">
-        <v>167601200</v>
+        <v>169022200</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>46170</v>
+        <v>46178</v>
       </c>
       <c r="B233" t="n">
-        <v>214.0005798339844</v>
+        <v>205.1000061035156</v>
       </c>
       <c r="C233" t="n">
-        <v>215.2691056248748</v>
+        <v>214.8699951171875</v>
       </c>
       <c r="D233" t="n">
-        <v>210.9741084423121</v>
+        <v>204.3300018310547</v>
       </c>
       <c r="E233" t="n">
-        <v>211.03403615446</v>
+        <v>214.5299987792969</v>
       </c>
       <c r="F233" t="n">
-        <v>143996000</v>
+        <v>219655500</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>46171</v>
+        <v>46181</v>
       </c>
       <c r="B234" t="n">
-        <v>210.8942108154297</v>
+        <v>208.6399993896484</v>
       </c>
       <c r="C234" t="n">
-        <v>217.6063892667686</v>
+        <v>210.4700012207031</v>
       </c>
       <c r="D234" t="n">
-        <v>210.8842279432229</v>
+        <v>206</v>
       </c>
       <c r="E234" t="n">
-        <v>214.3302087418325</v>
+        <v>210.1799926757812</v>
       </c>
       <c r="F234" t="n">
-        <v>289410600</v>
+        <v>138372800</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>46174</v>
+        <v>46182</v>
       </c>
       <c r="B235" t="n">
-        <v>224.0988159179688</v>
+        <v>208.1900024414062</v>
       </c>
       <c r="C235" t="n">
-        <v>224.6082167237973</v>
+        <v>211.3999938964844</v>
       </c>
       <c r="D235" t="n">
-        <v>215.448893644638</v>
+        <v>199.3399963378906</v>
       </c>
       <c r="E235" t="n">
-        <v>215.4788575013911</v>
+        <v>210.6199951171875</v>
       </c>
       <c r="F235" t="n">
-        <v>212850700</v>
+        <v>180962500</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>46175</v>
+        <v>46183</v>
       </c>
       <c r="B236" t="n">
-        <v>222.5606079101562</v>
+        <v>200.4199981689453</v>
       </c>
       <c r="C236" t="n">
-        <v>232.0095863674792</v>
+        <v>207.2200012207031</v>
       </c>
       <c r="D236" t="n">
-        <v>221.0923180144814</v>
+        <v>199.9199981689453</v>
       </c>
       <c r="E236" t="n">
-        <v>226.9155175162366</v>
+        <v>204.4299926757812</v>
       </c>
       <c r="F236" t="n">
-        <v>193362900</v>
+        <v>161746600</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>46176</v>
+        <v>46184</v>
       </c>
       <c r="B237" t="n">
-        <v>214.5</v>
+        <v>204.8699951171875</v>
       </c>
       <c r="C237" t="n">
-        <v>222.5606126707563</v>
+        <v>205.6600036621094</v>
       </c>
       <c r="D237" t="n">
-        <v>214.2602739078757</v>
+        <v>199.5399932861328</v>
       </c>
       <c r="E237" t="n">
-        <v>221.4618871331354</v>
+        <v>201.4900054931641</v>
       </c>
       <c r="F237" t="n">
-        <v>160907000</v>
+        <v>158643200</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>46177</v>
+        <v>46185</v>
       </c>
       <c r="B238" t="n">
-        <v>218.6600036621094</v>
+        <v>205.1900024414062</v>
       </c>
       <c r="C238" t="n">
-        <v>221.6000061035156</v>
+        <v>207.0700073242188</v>
       </c>
       <c r="D238" t="n">
-        <v>210.9700012207031</v>
+        <v>203.4400024414062</v>
       </c>
       <c r="E238" t="n">
-        <v>213.9100036621094</v>
+        <v>204.8600006103516</v>
       </c>
       <c r="F238" t="n">
-        <v>169022200</v>
+        <v>112001800</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>46178</v>
+        <v>46188</v>
       </c>
       <c r="B239" t="n">
-        <v>205.1000061035156</v>
+        <v>212.4499969482422</v>
       </c>
       <c r="C239" t="n">
-        <v>214.8699951171875</v>
+        <v>212.7100067138672</v>
       </c>
       <c r="D239" t="n">
-        <v>204.3300018310547</v>
+        <v>208.3399963378906</v>
       </c>
       <c r="E239" t="n">
-        <v>214.5299987792969</v>
+        <v>208.9199981689453</v>
       </c>
       <c r="F239" t="n">
-        <v>219655500</v>
+        <v>149936700</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>46181</v>
+        <v>46189</v>
       </c>
       <c r="B240" t="n">
-        <v>208.6399993896484</v>
+        <v>207.4100036621094</v>
       </c>
       <c r="C240" t="n">
-        <v>210.4700012207031</v>
+        <v>211.4900054931641</v>
       </c>
       <c r="D240" t="n">
-        <v>206</v>
+        <v>207.2899932861328</v>
       </c>
       <c r="E240" t="n">
-        <v>210.1799926757812</v>
+        <v>211.1799926757812</v>
       </c>
       <c r="F240" t="n">
-        <v>138372800</v>
+        <v>125694100</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>46182</v>
+        <v>46190</v>
       </c>
       <c r="B241" t="n">
-        <v>208.1900024414062</v>
+        <v>204.6499938964844</v>
       </c>
       <c r="C241" t="n">
-        <v>211.3999938964844</v>
+        <v>209.2100067138672</v>
       </c>
       <c r="D241" t="n">
-        <v>199.3399963378906</v>
+        <v>203.0800018310547</v>
       </c>
       <c r="E241" t="n">
-        <v>210.6199951171875</v>
+        <v>208.5299987792969</v>
       </c>
       <c r="F241" t="n">
-        <v>180962500</v>
+        <v>128363500</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>46183</v>
+        <v>46191</v>
       </c>
       <c r="B242" t="n">
-        <v>200.4199981689453</v>
+        <v>210.6900024414062</v>
       </c>
       <c r="C242" t="n">
-        <v>207.2200012207031</v>
+        <v>211.3899993896484</v>
       </c>
       <c r="D242" t="n">
-        <v>199.9199981689453</v>
+        <v>206.5</v>
       </c>
       <c r="E242" t="n">
-        <v>204.4299926757812</v>
+        <v>207.3300018310547</v>
       </c>
       <c r="F242" t="n">
-        <v>161746600</v>
+        <v>241272000</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>46184</v>
+        <v>46195</v>
       </c>
       <c r="B243" t="n">
-        <v>204.8699951171875</v>
+        <v>208.6499938964844</v>
       </c>
       <c r="C243" t="n">
-        <v>205.6600036621094</v>
+        <v>213.9900054931641</v>
       </c>
       <c r="D243" t="n">
-        <v>199.5399932861328</v>
+        <v>207.7200012207031</v>
       </c>
       <c r="E243" t="n">
-        <v>201.4900054931641</v>
+        <v>211.4400024414062</v>
       </c>
       <c r="F243" t="n">
-        <v>158643200</v>
+        <v>122041400</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>46185</v>
+        <v>46196</v>
       </c>
       <c r="B244" t="n">
-        <v>205.1900024414062</v>
+        <v>200.0399932861328</v>
       </c>
       <c r="C244" t="n">
-        <v>207.0700073242188</v>
+        <v>203.7700042724609</v>
       </c>
       <c r="D244" t="n">
-        <v>203.4400024414062</v>
+        <v>200</v>
       </c>
       <c r="E244" t="n">
-        <v>204.8600006103516</v>
+        <v>202.1699981689453</v>
       </c>
       <c r="F244" t="n">
-        <v>112001800</v>
+        <v>153496200</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>46188</v>
+        <v>46197</v>
       </c>
       <c r="B245" t="n">
-        <v>212.4499969482422</v>
+        <v>199</v>
       </c>
       <c r="C245" t="n">
-        <v>212.7100067138672</v>
+        <v>201.6699981689453</v>
       </c>
       <c r="D245" t="n">
-        <v>208.3399963378906</v>
+        <v>196.5800018310547</v>
       </c>
       <c r="E245" t="n">
-        <v>208.9199981689453</v>
+        <v>200.1199951171875</v>
       </c>
       <c r="F245" t="n">
-        <v>149936700</v>
+        <v>151810700</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>46189</v>
+        <v>46198</v>
       </c>
       <c r="B246" t="n">
-        <v>207.4100036621094</v>
+        <v>195.7400054931641</v>
       </c>
       <c r="C246" t="n">
-        <v>211.4900054931641</v>
+        <v>200.8000030517578</v>
       </c>
       <c r="D246" t="n">
-        <v>207.2899932861328</v>
+        <v>192.1300048828125</v>
       </c>
       <c r="E246" t="n">
-        <v>211.1799926757812</v>
+        <v>200.0800018310547</v>
       </c>
       <c r="F246" t="n">
-        <v>125694100</v>
+        <v>149550000</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>46190</v>
+        <v>46199</v>
       </c>
       <c r="B247" t="n">
-        <v>204.6499938964844</v>
+        <v>192.5299987792969</v>
       </c>
       <c r="C247" t="n">
-        <v>209.2100067138672</v>
+        <v>195.5500030517578</v>
       </c>
       <c r="D247" t="n">
-        <v>203.0800018310547</v>
+        <v>191.2200012207031</v>
       </c>
       <c r="E247" t="n">
-        <v>208.5299987792969</v>
+        <v>193.1199951171875</v>
       </c>
       <c r="F247" t="n">
-        <v>128363500</v>
+        <v>179304100</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>46191</v>
+        <v>46202</v>
       </c>
       <c r="B248" t="n">
-        <v>210.6900024414062</v>
+        <v>194.9700012207031</v>
       </c>
       <c r="C248" t="n">
-        <v>211.3899993896484</v>
+        <v>196.1799926757812</v>
       </c>
       <c r="D248" t="n">
-        <v>206.5</v>
+        <v>189.8000030517578</v>
       </c>
       <c r="E248" t="n">
-        <v>207.3300018310547</v>
+        <v>193.8500061035156</v>
       </c>
       <c r="F248" t="n">
-        <v>241272000</v>
+        <v>148835700</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B249" t="n">
-        <v>208.6499938964844</v>
+        <v>200.0899963378906</v>
       </c>
       <c r="C249" t="n">
-        <v>213.9900054931641</v>
+        <v>200.6300048828125</v>
       </c>
       <c r="D249" t="n">
-        <v>207.7200012207031</v>
+        <v>195.1100006103516</v>
       </c>
       <c r="E249" t="n">
-        <v>211.4400024414062</v>
+        <v>197.2400054931641</v>
       </c>
       <c r="F249" t="n">
-        <v>122041400</v>
+        <v>166476700</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>46196</v>
+        <v>46204</v>
       </c>
       <c r="B250" t="n">
-        <v>200.0399932861328</v>
+        <v>197.5800018310547</v>
       </c>
       <c r="C250" t="n">
-        <v>203.7700042724609</v>
+        <v>199.8500061035156</v>
       </c>
       <c r="D250" t="n">
-        <v>200</v>
+        <v>193.4499969482422</v>
       </c>
       <c r="E250" t="n">
-        <v>202.1699981689453</v>
+        <v>196.1999969482422</v>
       </c>
       <c r="F250" t="n">
-        <v>153496200</v>
+        <v>146147600</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>46197</v>
+        <v>46205</v>
       </c>
       <c r="B251" t="n">
-        <v>199</v>
+        <v>194.8300018310547</v>
       </c>
       <c r="C251" t="n">
-        <v>201.6699981689453</v>
+        <v>200.0599975585938</v>
       </c>
       <c r="D251" t="n">
-        <v>196.5800018310547</v>
+        <v>192.3500061035156</v>
       </c>
       <c r="E251" t="n">
-        <v>200.1199951171875</v>
+        <v>197.1399993896484</v>
       </c>
       <c r="F251" t="n">
-        <v>151810700</v>
+        <v>142068700</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
-        <v>46198</v>
+        <v>46209</v>
       </c>
       <c r="B252" t="n">
-        <v>195.7400054931641</v>
+        <v>195.5500030517578</v>
       </c>
       <c r="C252" t="n">
-        <v>200.7899932861328</v>
+        <v>197.5500030517578</v>
       </c>
       <c r="D252" t="n">
-        <v>192.1300048828125</v>
+        <v>194</v>
       </c>
       <c r="E252" t="n">
-        <v>200.0800018310547</v>
+        <v>194.3899993896484</v>
       </c>
       <c r="F252" t="n">
-        <v>138840761</v>
+        <v>96954806</v>
       </c>
     </row>
   </sheetData>
